--- a/DSA Checklist TUF+.xlsx
+++ b/DSA Checklist TUF+.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="393">
   <si>
     <r>
       <t/>
@@ -23,7 +23,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -39,7 +39,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -55,7 +55,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -71,7 +71,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -87,7 +87,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -102,7 +102,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -132,7 +132,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -141,13 +141,16 @@
     </r>
   </si>
   <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <t>Yes</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -162,7 +165,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -177,7 +180,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -192,7 +195,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -207,7 +210,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -222,7 +225,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -237,7 +240,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -252,7 +255,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -267,7 +270,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -282,7 +285,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -297,7 +300,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -312,7 +315,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -327,7 +330,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -357,7 +360,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -372,7 +375,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -387,7 +390,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -402,7 +405,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -417,7 +420,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -432,7 +435,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -462,7 +465,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -477,7 +480,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -492,7 +495,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -507,7 +510,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -522,7 +525,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -552,7 +555,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -567,7 +570,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -582,7 +585,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -597,7 +600,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -612,7 +615,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -627,7 +630,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -642,7 +645,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -657,7 +660,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -672,7 +675,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -687,7 +690,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -702,7 +705,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -717,7 +720,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -732,7 +735,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -747,7 +750,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -762,7 +765,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -777,7 +780,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -792,7 +795,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -807,7 +810,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -822,7 +825,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -837,7 +840,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -852,7 +855,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -867,7 +870,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -882,7 +885,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -897,7 +900,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -912,7 +915,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -927,7 +930,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -942,7 +945,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -957,7 +960,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -987,7 +990,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1002,7 +1005,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1017,7 +1020,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1032,7 +1035,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1047,7 +1050,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1062,7 +1065,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1077,7 +1080,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1092,7 +1095,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1107,7 +1110,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1122,7 +1125,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1137,7 +1140,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1152,7 +1155,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1167,7 +1170,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1182,7 +1185,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1197,7 +1200,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1212,7 +1215,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1227,7 +1230,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1242,7 +1245,7 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1257,7 +1260,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1272,7 +1275,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1287,7 +1290,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1302,7 +1305,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1317,7 +1320,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1332,7 +1335,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1347,7 +1350,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1362,7 +1365,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1377,7 +1380,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1392,7 +1395,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1407,7 +1410,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1422,7 +1425,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1437,7 +1440,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1452,7 +1455,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1467,7 +1470,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1482,7 +1485,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1497,7 +1500,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1512,7 +1515,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1527,7 +1530,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1542,7 +1545,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1557,7 +1560,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1572,7 +1575,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1587,7 +1590,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1617,7 +1620,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1632,7 +1635,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1647,7 +1650,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1662,7 +1665,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1677,7 +1680,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1692,7 +1695,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1707,7 +1710,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1722,7 +1725,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1737,7 +1740,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1752,7 +1755,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1767,7 +1770,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1782,7 +1785,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1797,7 +1800,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1812,7 +1815,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1827,7 +1830,7 @@
     <r>
       <rPr>
         <sz val="26"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1842,7 +1845,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1857,7 +1860,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1872,7 +1875,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1887,7 +1890,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1902,7 +1905,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1917,7 +1920,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1932,7 +1935,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1947,7 +1950,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1962,7 +1965,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1977,7 +1980,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1992,7 +1995,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2007,7 +2010,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2022,7 +2025,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2037,7 +2040,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2052,7 +2055,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2067,7 +2070,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2082,7 +2085,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2097,7 +2100,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2112,7 +2115,7 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2127,7 +2130,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2142,7 +2145,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2157,7 +2160,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2172,7 +2175,7 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2187,7 +2190,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2202,7 +2205,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2217,7 +2220,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2232,7 +2235,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2247,7 +2250,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2262,7 +2265,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2277,7 +2280,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2292,7 +2295,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2307,7 +2310,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2322,7 +2325,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2337,7 +2340,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2352,7 +2355,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2367,7 +2370,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2382,7 +2385,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2397,7 +2400,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2412,7 +2415,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2427,7 +2430,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2442,7 +2445,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2457,7 +2460,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2472,7 +2475,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2487,7 +2490,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2502,7 +2505,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2517,7 +2520,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2532,7 +2535,7 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2547,7 +2550,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2562,7 +2565,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2577,7 +2580,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2592,7 +2595,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2607,7 +2610,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2622,7 +2625,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2637,7 +2640,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2652,7 +2655,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2667,7 +2670,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2682,7 +2685,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2697,7 +2700,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2712,7 +2715,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2727,7 +2730,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2742,7 +2745,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2757,7 +2760,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2772,7 +2775,7 @@
     <r>
       <rPr>
         <sz val="24"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2787,7 +2790,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2802,7 +2805,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2817,7 +2820,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2832,7 +2835,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2847,7 +2850,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2862,7 +2865,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2877,7 +2880,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2892,7 +2895,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2907,7 +2910,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2922,7 +2925,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2937,7 +2940,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2952,7 +2955,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2967,7 +2970,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2982,7 +2985,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2997,7 +3000,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3012,7 +3015,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3027,7 +3030,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3042,7 +3045,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3057,7 +3060,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3072,7 +3075,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3087,7 +3090,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3102,7 +3105,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3117,7 +3120,7 @@
     <r>
       <rPr>
         <sz val="24"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3132,7 +3135,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3147,7 +3150,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3162,7 +3165,7 @@
     <r>
       <rPr>
         <sz val="24"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3177,7 +3180,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3192,7 +3195,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3207,7 +3210,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3222,7 +3225,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3237,7 +3240,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3252,7 +3255,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3267,7 +3270,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3282,7 +3285,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3297,7 +3300,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3312,7 +3315,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3327,7 +3330,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3342,7 +3345,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3357,7 +3360,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3372,7 +3375,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3387,7 +3390,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3402,7 +3405,7 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3417,7 +3420,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3432,7 +3435,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3447,7 +3450,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3462,7 +3465,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3477,7 +3480,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3492,7 +3495,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3507,7 +3510,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3522,7 +3525,7 @@
     <r>
       <rPr>
         <sz val="22"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3537,7 +3540,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3552,7 +3555,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3567,7 +3570,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3582,7 +3585,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3597,7 +3600,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3612,7 +3615,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3627,7 +3630,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3642,7 +3645,7 @@
     <r>
       <rPr>
         <sz val="22"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3657,7 +3660,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3672,7 +3675,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3687,7 +3690,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3702,7 +3705,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3717,7 +3720,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3732,7 +3735,7 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3747,7 +3750,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3762,7 +3765,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3777,7 +3780,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3792,7 +3795,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3807,7 +3810,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3822,7 +3825,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3837,7 +3840,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3852,7 +3855,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3867,7 +3870,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3882,7 +3885,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3897,7 +3900,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3912,7 +3915,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3927,7 +3930,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3942,7 +3945,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3957,7 +3960,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3972,7 +3975,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3987,7 +3990,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4002,7 +4005,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4017,7 +4020,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4032,7 +4035,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4047,7 +4050,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4062,7 +4065,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4077,7 +4080,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4092,7 +4095,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4107,7 +4110,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4122,7 +4125,7 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4137,7 +4140,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4152,7 +4155,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4167,7 +4170,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4182,7 +4185,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4197,7 +4200,7 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4212,7 +4215,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4227,7 +4230,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4242,7 +4245,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4257,7 +4260,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4272,7 +4275,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4287,7 +4290,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4302,7 +4305,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4317,7 +4320,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4332,7 +4335,7 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4347,7 +4350,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4362,7 +4365,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4377,7 +4380,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4392,7 +4395,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4407,7 +4410,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4422,7 +4425,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4437,7 +4440,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4452,7 +4455,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4467,7 +4470,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4482,7 +4485,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4497,7 +4500,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4508,7 +4511,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4523,7 +4526,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4538,7 +4541,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4553,7 +4556,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4568,7 +4571,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4583,7 +4586,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4598,7 +4601,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4613,7 +4616,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4628,7 +4631,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4643,7 +4646,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4658,7 +4661,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4673,7 +4676,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4688,7 +4691,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4703,7 +4706,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4718,7 +4721,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4733,7 +4736,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4748,7 +4751,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4763,7 +4766,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4778,7 +4781,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4793,7 +4796,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4808,7 +4811,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4823,7 +4826,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4838,7 +4841,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4853,7 +4856,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4868,7 +4871,7 @@
     <r>
       <rPr>
         <sz val="18"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4883,7 +4886,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4898,7 +4901,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4913,7 +4916,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4928,7 +4931,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4943,7 +4946,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4958,7 +4961,7 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4969,7 +4972,7 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4984,7 +4987,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4999,7 +5002,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5014,7 +5017,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5029,7 +5032,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5044,7 +5047,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5059,7 +5062,7 @@
     <r>
       <rPr>
         <sz val="22"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5074,7 +5077,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5089,7 +5092,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5104,7 +5107,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5119,7 +5122,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5134,7 +5137,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5149,7 +5152,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5164,7 +5167,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5179,7 +5182,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5194,7 +5197,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5209,7 +5212,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5224,7 +5227,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5239,7 +5242,7 @@
     <r>
       <rPr>
         <sz val="28"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5254,7 +5257,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5269,7 +5272,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5284,7 +5287,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5299,7 +5302,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5314,7 +5317,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5329,7 +5332,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5344,7 +5347,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5359,7 +5362,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5374,7 +5377,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5389,7 +5392,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5404,7 +5407,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5419,7 +5422,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5434,7 +5437,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5449,7 +5452,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5464,7 +5467,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5479,7 +5482,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5494,7 +5497,7 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5509,7 +5512,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5524,7 +5527,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5539,7 +5542,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5554,7 +5557,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5569,7 +5572,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5584,7 +5587,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5599,7 +5602,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5614,7 +5617,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5629,7 +5632,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5644,7 +5647,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5659,7 +5662,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5674,7 +5677,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5689,7 +5692,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5704,7 +5707,7 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5719,7 +5722,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5734,7 +5737,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5749,7 +5752,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5764,7 +5767,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5775,7 +5778,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5790,7 +5793,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5805,7 +5808,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5820,7 +5823,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5835,7 +5838,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5850,7 +5853,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5865,7 +5868,7 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5880,7 +5883,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5895,7 +5898,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5910,7 +5913,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5925,7 +5928,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -5939,7 +5942,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5950,97 +5953,91 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="20"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="24"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="36"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="26"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="18"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="28"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -6262,7 +6259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="154">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6282,12 +6279,12 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -6303,22 +6300,22 @@
     <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
@@ -6333,13 +6330,13 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="8" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="8" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
@@ -6366,6 +6363,237 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="8" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="8" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="9" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="9" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="9" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="9" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="14" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="10" applyFont="1" fillId="14" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="11" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="11" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="9" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="9" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="12" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="12" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="10" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="10" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="10" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="10" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="10" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="10" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="13" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="13" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="13" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="13" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6375,139 +6603,100 @@
     <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="11" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="11" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="9" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="9" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="14" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="14" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="14" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="18" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="18" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="18" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="15" applyFont="1" fillId="19" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="10" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="15" applyFont="1" fillId="19" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="10" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="15" applyFont="1" fillId="19" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="10" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="10" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="14" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="11" applyFont="1" fillId="14" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="21" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="21" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="12" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="12" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="10" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="10" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="13" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="13" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="11" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="11" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="11" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="11" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
@@ -6519,211 +6708,13 @@
     <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="11" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="14" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="14" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="10" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="14" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="14" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="14" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="14" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="12" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="12" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="15" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="15" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="15" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="18" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="18" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="18" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="16" applyFont="1" fillId="19" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="16" applyFont="1" fillId="19" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="16" applyFont="1" fillId="19" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="21" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="21" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="12" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="12" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="11" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="11" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="10" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -7034,11 +7025,11 @@
   <dimension ref="A1:E352"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="155" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="155" width="61.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="155" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="155" width="17.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="155" width="8.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="153" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="153" width="61.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="153" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="153" width="17.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="153" width="8.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
@@ -7074,225 +7065,237 @@
       <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A4" s="9"/>
       <c r="B4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A5" s="9"/>
       <c r="B5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A6" s="9"/>
       <c r="B6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+        <v>11</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A7" s="9"/>
       <c r="B7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A8" s="9"/>
       <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A9" s="9"/>
       <c r="B9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+        <v>14</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A10" s="9"/>
       <c r="B10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+        <v>15</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A11" s="9"/>
       <c r="B11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A12" s="9"/>
       <c r="B12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+        <v>17</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A13" s="9"/>
       <c r="B13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A14" s="9"/>
       <c r="B14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+        <v>19</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A15" s="9"/>
       <c r="B15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
+        <v>20</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A16" s="10"/>
       <c r="B16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A17" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A18" s="12"/>
       <c r="B18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+        <v>24</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A19" s="12"/>
       <c r="B19" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
+        <v>25</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A20" s="12"/>
       <c r="B20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+        <v>26</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A21" s="12"/>
       <c r="B21" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+        <v>27</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A22" s="13"/>
       <c r="B22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+        <v>28</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A23" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+        <v>30</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A24" s="15"/>
       <c r="B24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+        <v>31</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A25" s="15"/>
       <c r="B25" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+        <v>32</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A26" s="16"/>
       <c r="B26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+        <v>33</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="30.75" customFormat="1" s="1">
       <c r="A27" s="4"/>
       <c r="B27" s="17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -7300,203 +7303,203 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A28" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+        <v>36</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A29" s="19"/>
       <c r="B29" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A30" s="19"/>
       <c r="B30" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A31" s="19"/>
       <c r="B31" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+        <v>39</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A32" s="19"/>
       <c r="B32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
+        <v>40</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A33" s="19"/>
       <c r="B33" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A34" s="19"/>
       <c r="B34" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
+        <v>42</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A35" s="19"/>
       <c r="B35" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
+        <v>43</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A36" s="19"/>
       <c r="B36" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
+        <v>44</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A37" s="19"/>
       <c r="B37" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
+        <v>45</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A38" s="19"/>
       <c r="B38" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
+        <v>46</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A39" s="19"/>
       <c r="B39" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
+        <v>47</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A40" s="19"/>
       <c r="B40" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
+        <v>48</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A41" s="19"/>
       <c r="B41" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
+        <v>49</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A42" s="19"/>
       <c r="B42" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
+        <v>50</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A43" s="19"/>
       <c r="B43" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
+        <v>51</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A44" s="19"/>
       <c r="B44" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
+        <v>52</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A45" s="19"/>
       <c r="B45" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
+        <v>53</v>
+      </c>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A46" s="20"/>
       <c r="B46" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
+        <v>54</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A47" s="21"/>
       <c r="B47" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
+        <v>55</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A48" s="21"/>
       <c r="B48" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
+        <v>56</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A49" s="21"/>
       <c r="B49" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
+        <v>57</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A50" s="21"/>
@@ -7516,420 +7519,420 @@
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A51" s="21"/>
       <c r="B51" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
+        <v>58</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A52" s="21"/>
       <c r="B52" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A53" s="21"/>
       <c r="B53" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
+        <v>60</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A54" s="21"/>
       <c r="B54" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
+        <v>61</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A55" s="22"/>
       <c r="B55" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
+        <v>62</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A56" s="23"/>
       <c r="B56" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
+        <v>63</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A57" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
+        <v>65</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A58" s="25"/>
       <c r="B58" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
+        <v>66</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A59" s="25"/>
       <c r="B59" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
+        <v>67</v>
+      </c>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A60" s="25"/>
       <c r="B60" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
+        <v>68</v>
+      </c>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A61" s="25"/>
       <c r="B61" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
+        <v>69</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A62" s="25"/>
       <c r="B62" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
+        <v>70</v>
+      </c>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A63" s="25"/>
       <c r="B63" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
+        <v>71</v>
+      </c>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A64" s="25"/>
       <c r="B64" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
+        <v>72</v>
+      </c>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A65" s="25"/>
       <c r="B65" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
+        <v>73</v>
+      </c>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A66" s="25"/>
       <c r="B66" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
+        <v>74</v>
+      </c>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A67" s="25"/>
       <c r="B67" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
+        <v>75</v>
+      </c>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A68" s="25"/>
       <c r="B68" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
+        <v>76</v>
+      </c>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A69" s="25"/>
       <c r="B69" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
+        <v>77</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A70" s="25"/>
       <c r="B70" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
+        <v>78</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A71" s="25"/>
       <c r="B71" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
+        <v>79</v>
+      </c>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A72" s="25"/>
       <c r="B72" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
+        <v>80</v>
+      </c>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A73" s="26"/>
       <c r="B73" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A74" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
+        <v>83</v>
+      </c>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A75" s="28"/>
       <c r="B75" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
+        <v>84</v>
+      </c>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A76" s="28"/>
       <c r="B76" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
+        <v>85</v>
+      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A77" s="28"/>
       <c r="B77" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A78" s="28"/>
       <c r="B78" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A79" s="28"/>
       <c r="B79" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
+        <v>88</v>
+      </c>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A80" s="28"/>
       <c r="B80" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
+        <v>89</v>
+      </c>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A81" s="28"/>
       <c r="B81" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A82" s="28"/>
       <c r="B82" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
+        <v>91</v>
+      </c>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A83" s="28"/>
       <c r="B83" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
+        <v>92</v>
+      </c>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A84" s="28"/>
       <c r="B84" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
+        <v>93</v>
+      </c>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A85" s="29"/>
       <c r="B85" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
+        <v>94</v>
+      </c>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A86" s="30"/>
       <c r="B86" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
+        <v>95</v>
+      </c>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A87" s="31"/>
       <c r="B87" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
+        <v>96</v>
+      </c>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A88" s="31"/>
       <c r="B88" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
+        <v>97</v>
+      </c>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A89" s="31"/>
       <c r="B89" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
+        <v>98</v>
+      </c>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A90" s="31"/>
       <c r="B90" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
+        <v>99</v>
+      </c>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A91" s="31"/>
       <c r="B91" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
+        <v>100</v>
+      </c>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A92" s="31"/>
       <c r="B92" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
+        <v>101</v>
+      </c>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A93" s="32"/>
       <c r="B93" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
+        <v>102</v>
+      </c>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A94" s="31"/>
       <c r="B94" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
+        <v>103</v>
+      </c>
+      <c r="C94" s="7"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A95" s="33"/>
       <c r="B95" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
+        <v>104</v>
+      </c>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A96" s="34"/>
       <c r="B96" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
+        <v>105</v>
+      </c>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A97" s="2" t="s">
@@ -7950,437 +7953,437 @@
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A98" s="35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
+        <v>107</v>
+      </c>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A99" s="36"/>
       <c r="B99" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
+        <v>108</v>
+      </c>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A100" s="36"/>
       <c r="B100" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
+        <v>109</v>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A101" s="36"/>
       <c r="B101" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
+        <v>110</v>
+      </c>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A102" s="37"/>
       <c r="B102" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
+        <v>111</v>
+      </c>
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A103" s="38" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
+        <v>113</v>
+      </c>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A104" s="39"/>
       <c r="B104" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
+        <v>114</v>
+      </c>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A105" s="39"/>
       <c r="B105" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
+        <v>115</v>
+      </c>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A106" s="39"/>
       <c r="B106" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
+        <v>116</v>
+      </c>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A107" s="39"/>
       <c r="B107" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
+        <v>117</v>
+      </c>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A108" s="39"/>
       <c r="B108" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
+        <v>118</v>
+      </c>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A109" s="39"/>
       <c r="B109" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
+        <v>119</v>
+      </c>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A110" s="40"/>
       <c r="B110" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
+        <v>120</v>
+      </c>
+      <c r="C110" s="7"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A111" s="41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
+        <v>122</v>
+      </c>
+      <c r="C111" s="7"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A112" s="42"/>
       <c r="B112" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
+        <v>123</v>
+      </c>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A113" s="42"/>
       <c r="B113" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
+        <v>124</v>
+      </c>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A114" s="42"/>
       <c r="B114" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
+        <v>125</v>
+      </c>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A115" s="42"/>
       <c r="B115" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
+        <v>126</v>
+      </c>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A116" s="43"/>
       <c r="B116" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C116" s="8"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
+        <v>127</v>
+      </c>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A117" s="44" t="s">
-        <v>127</v>
+      <c r="A117" s="30" t="s">
+        <v>128</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
+        <v>129</v>
+      </c>
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A118" s="45"/>
+      <c r="A118" s="33"/>
       <c r="B118" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
+        <v>130</v>
+      </c>
+      <c r="C118" s="7"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A119" s="46" t="s">
-        <v>130</v>
+      <c r="A119" s="44" t="s">
+        <v>131</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
+        <v>132</v>
+      </c>
+      <c r="C119" s="7"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A120" s="47"/>
+      <c r="A120" s="45"/>
       <c r="B120" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
+        <v>133</v>
+      </c>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A121" s="47"/>
+      <c r="A121" s="45"/>
       <c r="B121" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
+        <v>134</v>
+      </c>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A122" s="47"/>
+      <c r="A122" s="45"/>
       <c r="B122" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
+        <v>135</v>
+      </c>
+      <c r="C122" s="7"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A123" s="47"/>
+      <c r="A123" s="45"/>
       <c r="B123" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
+        <v>136</v>
+      </c>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A124" s="47"/>
+      <c r="A124" s="45"/>
       <c r="B124" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
+        <v>137</v>
+      </c>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A125" s="47"/>
+      <c r="A125" s="45"/>
       <c r="B125" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
+        <v>138</v>
+      </c>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A126" s="48"/>
+      <c r="A126" s="46"/>
       <c r="B126" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
+        <v>139</v>
+      </c>
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A127" s="49" t="s">
-        <v>139</v>
+      <c r="A127" s="47" t="s">
+        <v>140</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
+        <v>141</v>
+      </c>
+      <c r="C127" s="7"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A128" s="50"/>
+      <c r="A128" s="48"/>
       <c r="B128" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
+        <v>142</v>
+      </c>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A129" s="51"/>
+      <c r="A129" s="49"/>
       <c r="B129" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
+        <v>143</v>
+      </c>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A130" s="52" t="s">
-        <v>143</v>
+      <c r="A130" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
+        <v>145</v>
+      </c>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A131" s="53"/>
+      <c r="A131" s="51"/>
       <c r="B131" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
+        <v>146</v>
+      </c>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A132" s="53"/>
+      <c r="A132" s="51"/>
       <c r="B132" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A133" s="53"/>
+      <c r="A133" s="51"/>
       <c r="B133" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
+        <v>148</v>
+      </c>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A134" s="53"/>
+      <c r="A134" s="51"/>
       <c r="B134" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
+        <v>149</v>
+      </c>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A135" s="54"/>
+      <c r="A135" s="52"/>
       <c r="B135" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
+        <v>150</v>
+      </c>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A136" s="55" t="s">
-        <v>150</v>
+      <c r="A136" s="53" t="s">
+        <v>151</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A137" s="56"/>
+      <c r="A137" s="54"/>
       <c r="B137" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
+        <v>153</v>
+      </c>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A138" s="57" t="s">
-        <v>153</v>
+      <c r="A138" s="55" t="s">
+        <v>154</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
+        <v>155</v>
+      </c>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A139" s="58"/>
+      <c r="A139" s="56"/>
       <c r="B139" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
-      <c r="E139" s="8"/>
+        <v>156</v>
+      </c>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A140" s="59" t="s">
-        <v>156</v>
+      <c r="A140" s="57" t="s">
+        <v>157</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
+        <v>158</v>
+      </c>
+      <c r="C140" s="7"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A141" s="58"/>
+      <c r="A141" s="56"/>
       <c r="B141" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
-      <c r="E141" s="8"/>
+        <v>159</v>
+      </c>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A142" s="58"/>
+      <c r="A142" s="56"/>
       <c r="B142" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C142" s="8"/>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
+        <v>160</v>
+      </c>
+      <c r="C142" s="7"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A143" s="60"/>
+      <c r="A143" s="58"/>
       <c r="B143" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
+        <v>161</v>
+      </c>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A144" s="2" t="s">
@@ -8400,434 +8403,434 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A145" s="61" t="s">
-        <v>161</v>
+      <c r="A145" s="59" t="s">
+        <v>162</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
+        <v>163</v>
+      </c>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A146" s="62"/>
+      <c r="A146" s="60"/>
       <c r="B146" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C146" s="8"/>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
+        <v>164</v>
+      </c>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A147" s="62"/>
+      <c r="A147" s="60"/>
       <c r="B147" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
-      <c r="E147" s="8"/>
+        <v>165</v>
+      </c>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A148" s="62"/>
+      <c r="A148" s="60"/>
       <c r="B148" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="C148" s="8"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="8"/>
+        <v>166</v>
+      </c>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A149" s="63"/>
+      <c r="A149" s="61"/>
       <c r="B149" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
-      <c r="E149" s="8"/>
+        <v>167</v>
+      </c>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A150" s="64" t="s">
-        <v>167</v>
+      <c r="A150" s="62" t="s">
+        <v>168</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C150" s="8"/>
-      <c r="D150" s="8"/>
-      <c r="E150" s="8"/>
+        <v>169</v>
+      </c>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A151" s="65"/>
+      <c r="A151" s="63"/>
       <c r="B151" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C151" s="8"/>
-      <c r="D151" s="8"/>
-      <c r="E151" s="8"/>
+        <v>170</v>
+      </c>
+      <c r="C151" s="7"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A152" s="65"/>
+      <c r="A152" s="63"/>
       <c r="B152" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C152" s="8"/>
-      <c r="D152" s="8"/>
-      <c r="E152" s="8"/>
+        <v>171</v>
+      </c>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A153" s="65"/>
+      <c r="A153" s="63"/>
       <c r="B153" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C153" s="8"/>
-      <c r="D153" s="8"/>
-      <c r="E153" s="8"/>
+        <v>172</v>
+      </c>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A154" s="65"/>
+      <c r="A154" s="63"/>
       <c r="B154" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C154" s="8"/>
-      <c r="D154" s="8"/>
-      <c r="E154" s="8"/>
+        <v>173</v>
+      </c>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A155" s="65"/>
+      <c r="A155" s="63"/>
       <c r="B155" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C155" s="8"/>
-      <c r="D155" s="8"/>
-      <c r="E155" s="8"/>
+        <v>174</v>
+      </c>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A156" s="65"/>
+      <c r="A156" s="63"/>
       <c r="B156" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="C156" s="8"/>
-      <c r="D156" s="8"/>
-      <c r="E156" s="8"/>
+        <v>175</v>
+      </c>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A157" s="66"/>
+      <c r="A157" s="64"/>
       <c r="B157" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
+        <v>176</v>
+      </c>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A158" s="67" t="s">
-        <v>176</v>
+      <c r="A158" s="65" t="s">
+        <v>177</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C158" s="8"/>
-      <c r="D158" s="8"/>
-      <c r="E158" s="8"/>
+        <v>178</v>
+      </c>
+      <c r="C158" s="7"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A159" s="68"/>
+      <c r="A159" s="66"/>
       <c r="B159" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
-      <c r="E159" s="8"/>
+        <v>179</v>
+      </c>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A160" s="68"/>
+      <c r="A160" s="66"/>
       <c r="B160" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C160" s="8"/>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
+        <v>180</v>
+      </c>
+      <c r="C160" s="7"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A161" s="68"/>
+      <c r="A161" s="66"/>
       <c r="B161" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
-      <c r="E161" s="8"/>
+        <v>181</v>
+      </c>
+      <c r="C161" s="7"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A162" s="68"/>
+      <c r="A162" s="66"/>
       <c r="B162" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C162" s="8"/>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
+        <v>182</v>
+      </c>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A163" s="69"/>
+      <c r="A163" s="67"/>
       <c r="B163" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
+        <v>183</v>
+      </c>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A164" s="70" t="s">
-        <v>183</v>
+      <c r="A164" s="68" t="s">
+        <v>184</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C164" s="8"/>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8"/>
+        <v>185</v>
+      </c>
+      <c r="C164" s="7"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A165" s="71"/>
+      <c r="A165" s="69"/>
       <c r="B165" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
+        <v>186</v>
+      </c>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A166" s="71"/>
+      <c r="A166" s="69"/>
       <c r="B166" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C166" s="8"/>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
+        <v>187</v>
+      </c>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A167" s="71"/>
+      <c r="A167" s="69"/>
       <c r="B167" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8"/>
+        <v>188</v>
+      </c>
+      <c r="C167" s="7"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A168" s="71"/>
+      <c r="A168" s="69"/>
       <c r="B168" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C168" s="8"/>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8"/>
+        <v>189</v>
+      </c>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A169" s="71"/>
+      <c r="A169" s="69"/>
       <c r="B169" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
-      <c r="E169" s="8"/>
+        <v>190</v>
+      </c>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A170" s="71"/>
+      <c r="A170" s="69"/>
       <c r="B170" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C170" s="8"/>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
+        <v>191</v>
+      </c>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A171" s="71"/>
+      <c r="A171" s="69"/>
       <c r="B171" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
-      <c r="E171" s="8"/>
+        <v>192</v>
+      </c>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A172" s="72"/>
+      <c r="A172" s="70"/>
       <c r="B172" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
+        <v>193</v>
+      </c>
+      <c r="C172" s="7"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A173" s="73" t="s">
-        <v>193</v>
+      <c r="A173" s="71" t="s">
+        <v>194</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
-      <c r="E173" s="8"/>
+        <v>195</v>
+      </c>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A174" s="74"/>
+      <c r="A174" s="72"/>
       <c r="B174" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C174" s="8"/>
-      <c r="D174" s="8"/>
-      <c r="E174" s="8"/>
+        <v>196</v>
+      </c>
+      <c r="C174" s="7"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A175" s="74"/>
+      <c r="A175" s="72"/>
       <c r="B175" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
-      <c r="E175" s="8"/>
+        <v>197</v>
+      </c>
+      <c r="C175" s="7"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A176" s="74"/>
+      <c r="A176" s="72"/>
       <c r="B176" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
+        <v>198</v>
+      </c>
+      <c r="C176" s="7"/>
+      <c r="D176" s="7"/>
+      <c r="E176" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A177" s="74"/>
+      <c r="A177" s="72"/>
       <c r="B177" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
+        <v>199</v>
+      </c>
+      <c r="C177" s="7"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A178" s="75"/>
+      <c r="A178" s="73"/>
       <c r="B178" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
+        <v>200</v>
+      </c>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A179" s="38" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
+        <v>201</v>
+      </c>
+      <c r="C179" s="7"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A180" s="39"/>
       <c r="B180" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
-      <c r="E180" s="8"/>
+        <v>202</v>
+      </c>
+      <c r="C180" s="7"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A181" s="39"/>
       <c r="B181" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
-      <c r="E181" s="8"/>
+        <v>203</v>
+      </c>
+      <c r="C181" s="7"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A182" s="39"/>
       <c r="B182" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
+        <v>204</v>
+      </c>
+      <c r="C182" s="7"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A183" s="39"/>
       <c r="B183" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
-      <c r="E183" s="8"/>
+        <v>205</v>
+      </c>
+      <c r="C183" s="7"/>
+      <c r="D183" s="7"/>
+      <c r="E183" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A184" s="40"/>
       <c r="B184" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
+        <v>206</v>
+      </c>
+      <c r="C184" s="7"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A185" s="76" t="s">
-        <v>206</v>
+      <c r="A185" s="74" t="s">
+        <v>207</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
-      <c r="E185" s="8"/>
+        <v>208</v>
+      </c>
+      <c r="C185" s="7"/>
+      <c r="D185" s="7"/>
+      <c r="E185" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A186" s="77"/>
+      <c r="A186" s="75"/>
       <c r="B186" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
+        <v>209</v>
+      </c>
+      <c r="C186" s="7"/>
+      <c r="D186" s="7"/>
+      <c r="E186" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A187" s="78" t="s">
-        <v>209</v>
+      <c r="A187" s="76" t="s">
+        <v>210</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
+        <v>211</v>
+      </c>
+      <c r="C187" s="7"/>
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A188" s="77"/>
+      <c r="A188" s="75"/>
       <c r="B188" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="C188" s="8"/>
-      <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
+        <v>212</v>
+      </c>
+      <c r="C188" s="7"/>
+      <c r="D188" s="7"/>
+      <c r="E188" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A189" s="77"/>
+      <c r="A189" s="75"/>
       <c r="B189" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
-      <c r="E189" s="8"/>
+        <v>213</v>
+      </c>
+      <c r="C189" s="7"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A190" s="79"/>
+      <c r="A190" s="77"/>
       <c r="B190" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
+        <v>214</v>
+      </c>
+      <c r="C190" s="7"/>
+      <c r="D190" s="7"/>
+      <c r="E190" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A191" s="2" t="s">
@@ -8847,407 +8850,407 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A192" s="76" t="s">
-        <v>183</v>
+      <c r="A192" s="74" t="s">
+        <v>184</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
+        <v>215</v>
+      </c>
+      <c r="C192" s="7"/>
+      <c r="D192" s="7"/>
+      <c r="E192" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A193" s="77"/>
+      <c r="A193" s="75"/>
       <c r="B193" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
-      <c r="E193" s="8"/>
+        <v>216</v>
+      </c>
+      <c r="C193" s="7"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A194" s="77"/>
+      <c r="A194" s="75"/>
       <c r="B194" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8"/>
+        <v>217</v>
+      </c>
+      <c r="C194" s="7"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A195" s="77"/>
+      <c r="A195" s="75"/>
       <c r="B195" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
-      <c r="E195" s="8"/>
+        <v>218</v>
+      </c>
+      <c r="C195" s="7"/>
+      <c r="D195" s="7"/>
+      <c r="E195" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A196" s="77"/>
+      <c r="A196" s="75"/>
       <c r="B196" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="C196" s="8"/>
-      <c r="D196" s="8"/>
-      <c r="E196" s="8"/>
+        <v>219</v>
+      </c>
+      <c r="C196" s="7"/>
+      <c r="D196" s="7"/>
+      <c r="E196" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A197" s="79"/>
+      <c r="A197" s="77"/>
       <c r="B197" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C197" s="8"/>
-      <c r="D197" s="8"/>
-      <c r="E197" s="8"/>
+        <v>220</v>
+      </c>
+      <c r="C197" s="7"/>
+      <c r="D197" s="7"/>
+      <c r="E197" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A198" s="80" t="s">
-        <v>220</v>
+      <c r="A198" s="78" t="s">
+        <v>221</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C198" s="8"/>
-      <c r="D198" s="8"/>
-      <c r="E198" s="8"/>
+        <v>222</v>
+      </c>
+      <c r="C198" s="7"/>
+      <c r="D198" s="7"/>
+      <c r="E198" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A199" s="81"/>
+      <c r="A199" s="79"/>
       <c r="B199" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
-      <c r="E199" s="8"/>
+        <v>223</v>
+      </c>
+      <c r="C199" s="7"/>
+      <c r="D199" s="7"/>
+      <c r="E199" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A200" s="81"/>
+      <c r="A200" s="79"/>
       <c r="B200" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C200" s="8"/>
-      <c r="D200" s="8"/>
-      <c r="E200" s="8"/>
+        <v>224</v>
+      </c>
+      <c r="C200" s="7"/>
+      <c r="D200" s="7"/>
+      <c r="E200" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A201" s="82"/>
+      <c r="A201" s="80"/>
       <c r="B201" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C201" s="8"/>
-      <c r="D201" s="8"/>
-      <c r="E201" s="8"/>
+        <v>225</v>
+      </c>
+      <c r="C201" s="7"/>
+      <c r="D201" s="7"/>
+      <c r="E201" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A202" s="64" t="s">
-        <v>225</v>
+      <c r="A202" s="62" t="s">
+        <v>226</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="C202" s="8"/>
-      <c r="D202" s="8"/>
-      <c r="E202" s="8"/>
+        <v>227</v>
+      </c>
+      <c r="C202" s="7"/>
+      <c r="D202" s="7"/>
+      <c r="E202" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A203" s="66"/>
+      <c r="A203" s="64"/>
       <c r="B203" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C203" s="8"/>
-      <c r="D203" s="8"/>
-      <c r="E203" s="8"/>
+        <v>228</v>
+      </c>
+      <c r="C203" s="7"/>
+      <c r="D203" s="7"/>
+      <c r="E203" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="30" customFormat="1" s="1">
       <c r="A204" s="4"/>
       <c r="B204" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A205" s="83" t="s">
-        <v>229</v>
+      <c r="A205" s="81" t="s">
+        <v>230</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C205" s="8"/>
-      <c r="D205" s="8"/>
-      <c r="E205" s="8"/>
+        <v>231</v>
+      </c>
+      <c r="C205" s="7"/>
+      <c r="D205" s="7"/>
+      <c r="E205" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A206" s="84"/>
+      <c r="A206" s="82"/>
       <c r="B206" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C206" s="8"/>
-      <c r="D206" s="8"/>
-      <c r="E206" s="8"/>
+        <v>232</v>
+      </c>
+      <c r="C206" s="7"/>
+      <c r="D206" s="7"/>
+      <c r="E206" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A207" s="85"/>
+      <c r="A207" s="83"/>
       <c r="B207" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C207" s="8"/>
-      <c r="D207" s="8"/>
-      <c r="E207" s="8"/>
+        <v>233</v>
+      </c>
+      <c r="C207" s="7"/>
+      <c r="D207" s="7"/>
+      <c r="E207" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A208" s="86" t="s">
-        <v>233</v>
+      <c r="A208" s="84" t="s">
+        <v>234</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C208" s="8"/>
-      <c r="D208" s="8"/>
-      <c r="E208" s="8"/>
+        <v>235</v>
+      </c>
+      <c r="C208" s="7"/>
+      <c r="D208" s="7"/>
+      <c r="E208" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A209" s="87"/>
+      <c r="A209" s="85"/>
       <c r="B209" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="C209" s="8"/>
-      <c r="D209" s="8"/>
-      <c r="E209" s="8"/>
+        <v>236</v>
+      </c>
+      <c r="C209" s="7"/>
+      <c r="D209" s="7"/>
+      <c r="E209" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A210" s="87"/>
+      <c r="A210" s="85"/>
       <c r="B210" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="C210" s="8"/>
-      <c r="D210" s="8"/>
-      <c r="E210" s="8"/>
+        <v>237</v>
+      </c>
+      <c r="C210" s="7"/>
+      <c r="D210" s="7"/>
+      <c r="E210" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A211" s="87"/>
+      <c r="A211" s="85"/>
       <c r="B211" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="C211" s="8"/>
-      <c r="D211" s="8"/>
-      <c r="E211" s="8"/>
+        <v>238</v>
+      </c>
+      <c r="C211" s="7"/>
+      <c r="D211" s="7"/>
+      <c r="E211" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A212" s="87"/>
+      <c r="A212" s="85"/>
       <c r="B212" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="C212" s="8"/>
-      <c r="D212" s="8"/>
-      <c r="E212" s="8"/>
+        <v>239</v>
+      </c>
+      <c r="C212" s="7"/>
+      <c r="D212" s="7"/>
+      <c r="E212" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A213" s="87"/>
+      <c r="A213" s="85"/>
       <c r="B213" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C213" s="8"/>
-      <c r="D213" s="8"/>
-      <c r="E213" s="8"/>
+        <v>240</v>
+      </c>
+      <c r="C213" s="7"/>
+      <c r="D213" s="7"/>
+      <c r="E213" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A214" s="88"/>
+      <c r="A214" s="86"/>
       <c r="B214" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="C214" s="8"/>
-      <c r="D214" s="8"/>
-      <c r="E214" s="8"/>
+        <v>241</v>
+      </c>
+      <c r="C214" s="7"/>
+      <c r="D214" s="7"/>
+      <c r="E214" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A215" s="89" t="s">
-        <v>241</v>
+      <c r="A215" s="87" t="s">
+        <v>242</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C215" s="8"/>
-      <c r="D215" s="8"/>
-      <c r="E215" s="8"/>
+        <v>243</v>
+      </c>
+      <c r="C215" s="7"/>
+      <c r="D215" s="7"/>
+      <c r="E215" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A216" s="90"/>
+      <c r="A216" s="88"/>
       <c r="B216" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C216" s="8"/>
-      <c r="D216" s="8"/>
-      <c r="E216" s="8"/>
+        <v>244</v>
+      </c>
+      <c r="C216" s="7"/>
+      <c r="D216" s="7"/>
+      <c r="E216" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A217" s="90"/>
+      <c r="A217" s="88"/>
       <c r="B217" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C217" s="8"/>
-      <c r="D217" s="8"/>
-      <c r="E217" s="8"/>
+        <v>245</v>
+      </c>
+      <c r="C217" s="7"/>
+      <c r="D217" s="7"/>
+      <c r="E217" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A218" s="91"/>
+      <c r="A218" s="89"/>
       <c r="B218" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C218" s="8"/>
-      <c r="D218" s="8"/>
-      <c r="E218" s="8"/>
+        <v>246</v>
+      </c>
+      <c r="C218" s="7"/>
+      <c r="D218" s="7"/>
+      <c r="E218" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="30" customFormat="1" s="1">
       <c r="A219" s="4"/>
       <c r="B219" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A220" s="92" t="s">
-        <v>247</v>
+      <c r="A220" s="90" t="s">
+        <v>248</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="C220" s="8"/>
-      <c r="D220" s="8"/>
-      <c r="E220" s="8"/>
+        <v>249</v>
+      </c>
+      <c r="C220" s="7"/>
+      <c r="D220" s="7"/>
+      <c r="E220" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A221" s="93"/>
+      <c r="A221" s="91"/>
       <c r="B221" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C221" s="8"/>
-      <c r="D221" s="8"/>
-      <c r="E221" s="8"/>
+        <v>250</v>
+      </c>
+      <c r="C221" s="7"/>
+      <c r="D221" s="7"/>
+      <c r="E221" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A222" s="93"/>
+      <c r="A222" s="91"/>
       <c r="B222" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="C222" s="8"/>
-      <c r="D222" s="8"/>
-      <c r="E222" s="8"/>
+        <v>251</v>
+      </c>
+      <c r="C222" s="7"/>
+      <c r="D222" s="7"/>
+      <c r="E222" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A223" s="93"/>
+      <c r="A223" s="91"/>
       <c r="B223" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="C223" s="8"/>
-      <c r="D223" s="8"/>
-      <c r="E223" s="8"/>
+        <v>252</v>
+      </c>
+      <c r="C223" s="7"/>
+      <c r="D223" s="7"/>
+      <c r="E223" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A224" s="93"/>
+      <c r="A224" s="91"/>
       <c r="B224" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="C224" s="8"/>
-      <c r="D224" s="8"/>
-      <c r="E224" s="8"/>
+        <v>253</v>
+      </c>
+      <c r="C224" s="7"/>
+      <c r="D224" s="7"/>
+      <c r="E224" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A225" s="93"/>
+      <c r="A225" s="91"/>
       <c r="B225" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="C225" s="8"/>
-      <c r="D225" s="8"/>
-      <c r="E225" s="8"/>
+        <v>254</v>
+      </c>
+      <c r="C225" s="7"/>
+      <c r="D225" s="7"/>
+      <c r="E225" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A226" s="93"/>
+      <c r="A226" s="91"/>
       <c r="B226" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C226" s="8"/>
-      <c r="D226" s="8"/>
-      <c r="E226" s="8"/>
+        <v>255</v>
+      </c>
+      <c r="C226" s="7"/>
+      <c r="D226" s="7"/>
+      <c r="E226" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A227" s="93"/>
+      <c r="A227" s="91"/>
       <c r="B227" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="C227" s="8"/>
-      <c r="D227" s="8"/>
-      <c r="E227" s="8"/>
+        <v>256</v>
+      </c>
+      <c r="C227" s="7"/>
+      <c r="D227" s="7"/>
+      <c r="E227" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A228" s="94"/>
+      <c r="A228" s="92"/>
       <c r="B228" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C228" s="8"/>
-      <c r="D228" s="8"/>
-      <c r="E228" s="8"/>
+        <v>257</v>
+      </c>
+      <c r="C228" s="7"/>
+      <c r="D228" s="7"/>
+      <c r="E228" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A229" s="95" t="s">
-        <v>257</v>
+      <c r="A229" s="93" t="s">
+        <v>258</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="C229" s="8"/>
-      <c r="D229" s="8"/>
-      <c r="E229" s="8"/>
+        <v>259</v>
+      </c>
+      <c r="C229" s="7"/>
+      <c r="D229" s="7"/>
+      <c r="E229" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="30" customFormat="1" s="1">
       <c r="A230" s="4"/>
       <c r="B230" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A231" s="96" t="s">
-        <v>260</v>
+      <c r="A231" s="94" t="s">
+        <v>261</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C231" s="8"/>
-      <c r="D231" s="8"/>
-      <c r="E231" s="8"/>
+        <v>262</v>
+      </c>
+      <c r="C231" s="7"/>
+      <c r="D231" s="7"/>
+      <c r="E231" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A232" s="97"/>
+      <c r="A232" s="95"/>
       <c r="B232" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C232" s="8"/>
-      <c r="D232" s="8"/>
-      <c r="E232" s="8"/>
+        <v>263</v>
+      </c>
+      <c r="C232" s="7"/>
+      <c r="D232" s="7"/>
+      <c r="E232" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A233" s="98"/>
+      <c r="A233" s="96"/>
       <c r="B233" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="C233" s="8"/>
-      <c r="D233" s="8"/>
-      <c r="E233" s="8"/>
+        <v>264</v>
+      </c>
+      <c r="C233" s="7"/>
+      <c r="D233" s="7"/>
+      <c r="E233" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A234" s="8"/>
-      <c r="B234" s="8"/>
-      <c r="C234" s="8"/>
-      <c r="D234" s="8"/>
-      <c r="E234" s="8"/>
+      <c r="A234" s="7"/>
+      <c r="B234" s="7"/>
+      <c r="C234" s="7"/>
+      <c r="D234" s="7"/>
+      <c r="E234" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A235" s="2" t="s">
@@ -9267,422 +9270,422 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A236" s="99" t="s">
-        <v>264</v>
+      <c r="A236" s="97" t="s">
+        <v>265</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="C236" s="8"/>
-      <c r="D236" s="8"/>
-      <c r="E236" s="8"/>
+        <v>266</v>
+      </c>
+      <c r="C236" s="7"/>
+      <c r="D236" s="7"/>
+      <c r="E236" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A237" s="100"/>
+      <c r="A237" s="98"/>
       <c r="B237" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="C237" s="8"/>
-      <c r="D237" s="8"/>
-      <c r="E237" s="8"/>
+        <v>267</v>
+      </c>
+      <c r="C237" s="7"/>
+      <c r="D237" s="7"/>
+      <c r="E237" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A238" s="100"/>
+      <c r="A238" s="98"/>
       <c r="B238" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C238" s="8"/>
-      <c r="D238" s="8"/>
-      <c r="E238" s="8"/>
+        <v>268</v>
+      </c>
+      <c r="C238" s="7"/>
+      <c r="D238" s="7"/>
+      <c r="E238" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A239" s="100"/>
+      <c r="A239" s="98"/>
       <c r="B239" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="C239" s="8"/>
-      <c r="D239" s="8"/>
-      <c r="E239" s="8"/>
+        <v>269</v>
+      </c>
+      <c r="C239" s="7"/>
+      <c r="D239" s="7"/>
+      <c r="E239" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A240" s="100"/>
+      <c r="A240" s="98"/>
       <c r="B240" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="C240" s="8"/>
-      <c r="D240" s="8"/>
-      <c r="E240" s="8"/>
+        <v>270</v>
+      </c>
+      <c r="C240" s="7"/>
+      <c r="D240" s="7"/>
+      <c r="E240" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A241" s="100"/>
+      <c r="A241" s="98"/>
       <c r="B241" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="C241" s="8"/>
-      <c r="D241" s="8"/>
-      <c r="E241" s="8"/>
+        <v>271</v>
+      </c>
+      <c r="C241" s="7"/>
+      <c r="D241" s="7"/>
+      <c r="E241" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A242" s="100"/>
+      <c r="A242" s="98"/>
       <c r="B242" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="C242" s="8"/>
-      <c r="D242" s="8"/>
-      <c r="E242" s="8"/>
+        <v>272</v>
+      </c>
+      <c r="C242" s="7"/>
+      <c r="D242" s="7"/>
+      <c r="E242" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A243" s="101"/>
+      <c r="A243" s="99"/>
       <c r="B243" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="C243" s="8"/>
-      <c r="D243" s="8"/>
-      <c r="E243" s="8"/>
+        <v>273</v>
+      </c>
+      <c r="C243" s="7"/>
+      <c r="D243" s="7"/>
+      <c r="E243" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A244" s="102" t="s">
-        <v>273</v>
+      <c r="A244" s="100" t="s">
+        <v>274</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C244" s="8"/>
-      <c r="D244" s="8"/>
-      <c r="E244" s="8"/>
+        <v>275</v>
+      </c>
+      <c r="C244" s="7"/>
+      <c r="D244" s="7"/>
+      <c r="E244" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A245" s="103"/>
+      <c r="A245" s="101"/>
       <c r="B245" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C245" s="8"/>
-      <c r="D245" s="8"/>
-      <c r="E245" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="C245" s="7"/>
+      <c r="D245" s="7"/>
+      <c r="E245" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A246" s="103"/>
+      <c r="A246" s="101"/>
       <c r="B246" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C246" s="8"/>
-      <c r="D246" s="8"/>
-      <c r="E246" s="8"/>
+        <v>277</v>
+      </c>
+      <c r="C246" s="7"/>
+      <c r="D246" s="7"/>
+      <c r="E246" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A247" s="104"/>
+      <c r="A247" s="102"/>
       <c r="B247" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C247" s="8"/>
-      <c r="D247" s="8"/>
-      <c r="E247" s="8"/>
+        <v>278</v>
+      </c>
+      <c r="C247" s="7"/>
+      <c r="D247" s="7"/>
+      <c r="E247" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A248" s="105" t="s">
-        <v>278</v>
+      <c r="A248" s="103" t="s">
+        <v>279</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C248" s="8"/>
-      <c r="D248" s="8"/>
-      <c r="E248" s="8"/>
+        <v>280</v>
+      </c>
+      <c r="C248" s="7"/>
+      <c r="D248" s="7"/>
+      <c r="E248" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A249" s="106"/>
+      <c r="A249" s="104"/>
       <c r="B249" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C249" s="8"/>
-      <c r="D249" s="8"/>
-      <c r="E249" s="8"/>
+        <v>281</v>
+      </c>
+      <c r="C249" s="7"/>
+      <c r="D249" s="7"/>
+      <c r="E249" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A250" s="106"/>
+      <c r="A250" s="104"/>
       <c r="B250" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="C250" s="8"/>
-      <c r="D250" s="8"/>
-      <c r="E250" s="8"/>
+        <v>282</v>
+      </c>
+      <c r="C250" s="7"/>
+      <c r="D250" s="7"/>
+      <c r="E250" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A251" s="106"/>
+      <c r="A251" s="104"/>
       <c r="B251" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="C251" s="8"/>
-      <c r="D251" s="8"/>
-      <c r="E251" s="8"/>
+        <v>283</v>
+      </c>
+      <c r="C251" s="7"/>
+      <c r="D251" s="7"/>
+      <c r="E251" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A252" s="106"/>
+      <c r="A252" s="104"/>
       <c r="B252" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C252" s="8"/>
-      <c r="D252" s="8"/>
-      <c r="E252" s="8"/>
+        <v>284</v>
+      </c>
+      <c r="C252" s="7"/>
+      <c r="D252" s="7"/>
+      <c r="E252" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A253" s="106"/>
+      <c r="A253" s="104"/>
       <c r="B253" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C253" s="8"/>
-      <c r="D253" s="8"/>
-      <c r="E253" s="8"/>
+        <v>285</v>
+      </c>
+      <c r="C253" s="7"/>
+      <c r="D253" s="7"/>
+      <c r="E253" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A254" s="106"/>
+      <c r="A254" s="104"/>
       <c r="B254" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="C254" s="8"/>
-      <c r="D254" s="8"/>
-      <c r="E254" s="8"/>
+        <v>286</v>
+      </c>
+      <c r="C254" s="7"/>
+      <c r="D254" s="7"/>
+      <c r="E254" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A255" s="107"/>
+      <c r="A255" s="105"/>
       <c r="B255" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="C255" s="8"/>
-      <c r="D255" s="8"/>
-      <c r="E255" s="8"/>
+        <v>287</v>
+      </c>
+      <c r="C255" s="7"/>
+      <c r="D255" s="7"/>
+      <c r="E255" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A256" s="108" t="s">
-        <v>287</v>
+      <c r="A256" s="106" t="s">
+        <v>288</v>
       </c>
       <c r="B256" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="C256" s="8"/>
-      <c r="D256" s="8"/>
-      <c r="E256" s="8"/>
+        <v>289</v>
+      </c>
+      <c r="C256" s="7"/>
+      <c r="D256" s="7"/>
+      <c r="E256" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A257" s="109"/>
+      <c r="A257" s="107"/>
       <c r="B257" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="C257" s="8"/>
-      <c r="D257" s="8"/>
-      <c r="E257" s="8"/>
+        <v>290</v>
+      </c>
+      <c r="C257" s="7"/>
+      <c r="D257" s="7"/>
+      <c r="E257" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A258" s="109"/>
+      <c r="A258" s="107"/>
       <c r="B258" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C258" s="8"/>
-      <c r="D258" s="8"/>
-      <c r="E258" s="8"/>
+        <v>291</v>
+      </c>
+      <c r="C258" s="7"/>
+      <c r="D258" s="7"/>
+      <c r="E258" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A259" s="109"/>
+      <c r="A259" s="107"/>
       <c r="B259" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="C259" s="8"/>
-      <c r="D259" s="8"/>
-      <c r="E259" s="8"/>
+        <v>292</v>
+      </c>
+      <c r="C259" s="7"/>
+      <c r="D259" s="7"/>
+      <c r="E259" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A260" s="109"/>
+      <c r="A260" s="107"/>
       <c r="B260" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C260" s="8"/>
-      <c r="D260" s="8"/>
-      <c r="E260" s="8"/>
+        <v>293</v>
+      </c>
+      <c r="C260" s="7"/>
+      <c r="D260" s="7"/>
+      <c r="E260" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A261" s="109"/>
+      <c r="A261" s="107"/>
       <c r="B261" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C261" s="8"/>
-      <c r="D261" s="8"/>
-      <c r="E261" s="8"/>
+        <v>294</v>
+      </c>
+      <c r="C261" s="7"/>
+      <c r="D261" s="7"/>
+      <c r="E261" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A262" s="109"/>
+      <c r="A262" s="107"/>
       <c r="B262" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="C262" s="8"/>
-      <c r="D262" s="8"/>
-      <c r="E262" s="8"/>
+        <v>295</v>
+      </c>
+      <c r="C262" s="7"/>
+      <c r="D262" s="7"/>
+      <c r="E262" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A263" s="109"/>
+      <c r="A263" s="107"/>
       <c r="B263" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C263" s="8"/>
-      <c r="D263" s="8"/>
-      <c r="E263" s="8"/>
+        <v>296</v>
+      </c>
+      <c r="C263" s="7"/>
+      <c r="D263" s="7"/>
+      <c r="E263" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A264" s="109"/>
+      <c r="A264" s="107"/>
       <c r="B264" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="C264" s="8"/>
-      <c r="D264" s="8"/>
-      <c r="E264" s="8"/>
+        <v>297</v>
+      </c>
+      <c r="C264" s="7"/>
+      <c r="D264" s="7"/>
+      <c r="E264" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A265" s="110"/>
+      <c r="A265" s="108"/>
       <c r="B265" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C265" s="8"/>
-      <c r="D265" s="8"/>
-      <c r="E265" s="8"/>
+        <v>298</v>
+      </c>
+      <c r="C265" s="7"/>
+      <c r="D265" s="7"/>
+      <c r="E265" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A266" s="111" t="s">
-        <v>298</v>
+      <c r="A266" s="109" t="s">
+        <v>299</v>
       </c>
       <c r="B266" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="C266" s="8"/>
-      <c r="D266" s="8"/>
-      <c r="E266" s="8"/>
+        <v>300</v>
+      </c>
+      <c r="C266" s="7"/>
+      <c r="D266" s="7"/>
+      <c r="E266" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A267" s="112"/>
+      <c r="A267" s="110"/>
       <c r="B267" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="C267" s="8"/>
-      <c r="D267" s="8"/>
-      <c r="E267" s="8"/>
+        <v>301</v>
+      </c>
+      <c r="C267" s="7"/>
+      <c r="D267" s="7"/>
+      <c r="E267" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A268" s="113"/>
+      <c r="A268" s="111"/>
       <c r="B268" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="C268" s="8"/>
-      <c r="D268" s="8"/>
-      <c r="E268" s="8"/>
+        <v>302</v>
+      </c>
+      <c r="C268" s="7"/>
+      <c r="D268" s="7"/>
+      <c r="E268" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A269" s="114" t="s">
-        <v>302</v>
+      <c r="A269" s="112" t="s">
+        <v>303</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="C269" s="8"/>
-      <c r="D269" s="8"/>
-      <c r="E269" s="8"/>
+        <v>304</v>
+      </c>
+      <c r="C269" s="7"/>
+      <c r="D269" s="7"/>
+      <c r="E269" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A270" s="115"/>
+      <c r="A270" s="113"/>
       <c r="B270" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="C270" s="8"/>
-      <c r="D270" s="8"/>
-      <c r="E270" s="8"/>
+        <v>305</v>
+      </c>
+      <c r="C270" s="7"/>
+      <c r="D270" s="7"/>
+      <c r="E270" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A271" s="115"/>
+      <c r="A271" s="113"/>
       <c r="B271" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="C271" s="8"/>
-      <c r="D271" s="8"/>
-      <c r="E271" s="8"/>
+        <v>306</v>
+      </c>
+      <c r="C271" s="7"/>
+      <c r="D271" s="7"/>
+      <c r="E271" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A272" s="115"/>
+      <c r="A272" s="113"/>
       <c r="B272" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="C272" s="8"/>
-      <c r="D272" s="8"/>
-      <c r="E272" s="8"/>
+        <v>307</v>
+      </c>
+      <c r="C272" s="7"/>
+      <c r="D272" s="7"/>
+      <c r="E272" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A273" s="116"/>
+      <c r="A273" s="114"/>
       <c r="B273" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="C273" s="8"/>
-      <c r="D273" s="8"/>
-      <c r="E273" s="8"/>
+        <v>308</v>
+      </c>
+      <c r="C273" s="7"/>
+      <c r="D273" s="7"/>
+      <c r="E273" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A274" s="117" t="s">
-        <v>308</v>
+      <c r="A274" s="115" t="s">
+        <v>309</v>
       </c>
       <c r="B274" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C274" s="8"/>
-      <c r="D274" s="8"/>
-      <c r="E274" s="8"/>
+        <v>310</v>
+      </c>
+      <c r="C274" s="7"/>
+      <c r="D274" s="7"/>
+      <c r="E274" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A275" s="118"/>
+      <c r="A275" s="116"/>
       <c r="B275" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="C275" s="8"/>
-      <c r="D275" s="8"/>
-      <c r="E275" s="8"/>
+        <v>311</v>
+      </c>
+      <c r="C275" s="7"/>
+      <c r="D275" s="7"/>
+      <c r="E275" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A276" s="119"/>
+      <c r="A276" s="117"/>
       <c r="B276" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="C276" s="8"/>
-      <c r="D276" s="8"/>
-      <c r="E276" s="8"/>
+        <v>312</v>
+      </c>
+      <c r="C276" s="7"/>
+      <c r="D276" s="7"/>
+      <c r="E276" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A277" s="8"/>
-      <c r="B277" s="8"/>
-      <c r="C277" s="8"/>
-      <c r="D277" s="8"/>
-      <c r="E277" s="8"/>
+      <c r="A277" s="7"/>
+      <c r="B277" s="7"/>
+      <c r="C277" s="7"/>
+      <c r="D277" s="7"/>
+      <c r="E277" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A278" s="8"/>
-      <c r="B278" s="8"/>
-      <c r="C278" s="8"/>
-      <c r="D278" s="8"/>
-      <c r="E278" s="8"/>
+      <c r="A278" s="7"/>
+      <c r="B278" s="7"/>
+      <c r="C278" s="7"/>
+      <c r="D278" s="7"/>
+      <c r="E278" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A279" s="8"/>
-      <c r="B279" s="8"/>
-      <c r="C279" s="8"/>
-      <c r="D279" s="8"/>
-      <c r="E279" s="8"/>
+      <c r="A279" s="7"/>
+      <c r="B279" s="7"/>
+      <c r="C279" s="7"/>
+      <c r="D279" s="7"/>
+      <c r="E279" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A280" s="8"/>
-      <c r="B280" s="8"/>
-      <c r="C280" s="8"/>
-      <c r="D280" s="8"/>
-      <c r="E280" s="8"/>
+      <c r="A280" s="7"/>
+      <c r="B280" s="7"/>
+      <c r="C280" s="7"/>
+      <c r="D280" s="7"/>
+      <c r="E280" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A281" s="8"/>
-      <c r="B281" s="8"/>
-      <c r="C281" s="8"/>
-      <c r="D281" s="8"/>
-      <c r="E281" s="8"/>
+      <c r="A281" s="7"/>
+      <c r="B281" s="7"/>
+      <c r="C281" s="7"/>
+      <c r="D281" s="7"/>
+      <c r="E281" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A282" s="3" t="s">
@@ -9704,421 +9707,421 @@
     <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="30" customFormat="1" s="1">
       <c r="A283" s="4"/>
       <c r="B283" s="17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C283" s="4"/>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A284" s="120" t="s">
-        <v>194</v>
+      <c r="A284" s="118" t="s">
+        <v>195</v>
       </c>
       <c r="B284" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C284" s="8"/>
-      <c r="D284" s="8"/>
-      <c r="E284" s="8"/>
+        <v>314</v>
+      </c>
+      <c r="C284" s="7"/>
+      <c r="D284" s="7"/>
+      <c r="E284" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A285" s="121" t="s">
-        <v>314</v>
+      <c r="A285" s="119" t="s">
+        <v>315</v>
       </c>
       <c r="B285" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="C285" s="8"/>
-      <c r="D285" s="8"/>
-      <c r="E285" s="8"/>
+        <v>316</v>
+      </c>
+      <c r="C285" s="7"/>
+      <c r="D285" s="7"/>
+      <c r="E285" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A286" s="122"/>
+      <c r="A286" s="120"/>
       <c r="B286" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="C286" s="8"/>
-      <c r="D286" s="8"/>
-      <c r="E286" s="8"/>
+        <v>317</v>
+      </c>
+      <c r="C286" s="7"/>
+      <c r="D286" s="7"/>
+      <c r="E286" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A287" s="122"/>
+      <c r="A287" s="120"/>
       <c r="B287" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="C287" s="8"/>
-      <c r="D287" s="8"/>
-      <c r="E287" s="8"/>
+        <v>318</v>
+      </c>
+      <c r="C287" s="7"/>
+      <c r="D287" s="7"/>
+      <c r="E287" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A288" s="122"/>
+      <c r="A288" s="120"/>
       <c r="B288" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C288" s="8"/>
-      <c r="D288" s="8"/>
-      <c r="E288" s="8"/>
+        <v>319</v>
+      </c>
+      <c r="C288" s="7"/>
+      <c r="D288" s="7"/>
+      <c r="E288" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A289" s="123"/>
+      <c r="A289" s="121"/>
       <c r="B289" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="C289" s="8"/>
-      <c r="D289" s="8"/>
-      <c r="E289" s="8"/>
+        <v>320</v>
+      </c>
+      <c r="C289" s="7"/>
+      <c r="D289" s="7"/>
+      <c r="E289" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A290" s="124" t="s">
-        <v>320</v>
+      <c r="A290" s="122" t="s">
+        <v>321</v>
       </c>
       <c r="B290" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C290" s="8"/>
-      <c r="D290" s="8"/>
-      <c r="E290" s="8"/>
+        <v>322</v>
+      </c>
+      <c r="C290" s="7"/>
+      <c r="D290" s="7"/>
+      <c r="E290" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A291" s="125" t="s">
-        <v>322</v>
+      <c r="A291" s="123" t="s">
+        <v>323</v>
       </c>
       <c r="B291" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C291" s="8"/>
-      <c r="D291" s="8"/>
-      <c r="E291" s="8"/>
+        <v>324</v>
+      </c>
+      <c r="C291" s="7"/>
+      <c r="D291" s="7"/>
+      <c r="E291" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A292" s="126"/>
+      <c r="A292" s="124"/>
       <c r="B292" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="C292" s="8"/>
-      <c r="D292" s="8"/>
-      <c r="E292" s="8"/>
+        <v>325</v>
+      </c>
+      <c r="C292" s="7"/>
+      <c r="D292" s="7"/>
+      <c r="E292" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A293" s="126"/>
+      <c r="A293" s="124"/>
       <c r="B293" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C293" s="8"/>
-      <c r="D293" s="8"/>
-      <c r="E293" s="8"/>
+        <v>326</v>
+      </c>
+      <c r="C293" s="7"/>
+      <c r="D293" s="7"/>
+      <c r="E293" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A294" s="126"/>
+      <c r="A294" s="124"/>
       <c r="B294" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="C294" s="8"/>
-      <c r="D294" s="8"/>
-      <c r="E294" s="8"/>
+        <v>327</v>
+      </c>
+      <c r="C294" s="7"/>
+      <c r="D294" s="7"/>
+      <c r="E294" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A295" s="127"/>
+      <c r="A295" s="125"/>
       <c r="B295" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C295" s="8"/>
-      <c r="D295" s="8"/>
-      <c r="E295" s="8"/>
+        <v>328</v>
+      </c>
+      <c r="C295" s="7"/>
+      <c r="D295" s="7"/>
+      <c r="E295" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A296" s="128" t="s">
-        <v>328</v>
+      <c r="A296" s="126" t="s">
+        <v>329</v>
       </c>
       <c r="B296" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C296" s="8"/>
-      <c r="D296" s="8"/>
-      <c r="E296" s="8"/>
+        <v>330</v>
+      </c>
+      <c r="C296" s="7"/>
+      <c r="D296" s="7"/>
+      <c r="E296" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A297" s="129"/>
+      <c r="A297" s="127"/>
       <c r="B297" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="C297" s="8"/>
-      <c r="D297" s="8"/>
-      <c r="E297" s="8"/>
+        <v>331</v>
+      </c>
+      <c r="C297" s="7"/>
+      <c r="D297" s="7"/>
+      <c r="E297" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A298" s="129"/>
+      <c r="A298" s="127"/>
       <c r="B298" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="C298" s="8"/>
-      <c r="D298" s="8"/>
-      <c r="E298" s="8"/>
+        <v>332</v>
+      </c>
+      <c r="C298" s="7"/>
+      <c r="D298" s="7"/>
+      <c r="E298" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A299" s="129"/>
+      <c r="A299" s="127"/>
       <c r="B299" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="C299" s="8"/>
-      <c r="D299" s="8"/>
-      <c r="E299" s="8"/>
+        <v>333</v>
+      </c>
+      <c r="C299" s="7"/>
+      <c r="D299" s="7"/>
+      <c r="E299" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A300" s="130"/>
+      <c r="A300" s="128"/>
       <c r="B300" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="C300" s="8"/>
-      <c r="D300" s="8"/>
-      <c r="E300" s="8"/>
+        <v>334</v>
+      </c>
+      <c r="C300" s="7"/>
+      <c r="D300" s="7"/>
+      <c r="E300" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A301" s="86" t="s">
-        <v>334</v>
+      <c r="A301" s="84" t="s">
+        <v>335</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="C301" s="8"/>
-      <c r="D301" s="8"/>
-      <c r="E301" s="8"/>
+        <v>336</v>
+      </c>
+      <c r="C301" s="7"/>
+      <c r="D301" s="7"/>
+      <c r="E301" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A302" s="87"/>
+      <c r="A302" s="85"/>
       <c r="B302" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="C302" s="8"/>
-      <c r="D302" s="8"/>
-      <c r="E302" s="8"/>
+        <v>337</v>
+      </c>
+      <c r="C302" s="7"/>
+      <c r="D302" s="7"/>
+      <c r="E302" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A303" s="87"/>
-      <c r="B303" s="131" t="s">
-        <v>337</v>
-      </c>
-      <c r="C303" s="132"/>
-      <c r="D303" s="133"/>
-      <c r="E303" s="8"/>
+      <c r="A303" s="85"/>
+      <c r="B303" s="129" t="s">
+        <v>338</v>
+      </c>
+      <c r="C303" s="130"/>
+      <c r="D303" s="131"/>
+      <c r="E303" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A304" s="87"/>
+      <c r="A304" s="85"/>
       <c r="B304" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C304" s="8"/>
-      <c r="D304" s="8"/>
-      <c r="E304" s="8"/>
+        <v>339</v>
+      </c>
+      <c r="C304" s="7"/>
+      <c r="D304" s="7"/>
+      <c r="E304" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A305" s="87"/>
+      <c r="A305" s="85"/>
       <c r="B305" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="C305" s="8"/>
-      <c r="D305" s="8"/>
-      <c r="E305" s="8"/>
+        <v>340</v>
+      </c>
+      <c r="C305" s="7"/>
+      <c r="D305" s="7"/>
+      <c r="E305" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A306" s="87"/>
+      <c r="A306" s="85"/>
       <c r="B306" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="C306" s="8"/>
-      <c r="D306" s="8"/>
-      <c r="E306" s="8"/>
+        <v>341</v>
+      </c>
+      <c r="C306" s="7"/>
+      <c r="D306" s="7"/>
+      <c r="E306" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A307" s="87"/>
+      <c r="A307" s="85"/>
       <c r="B307" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="C307" s="8"/>
-      <c r="D307" s="8"/>
-      <c r="E307" s="8"/>
+        <v>342</v>
+      </c>
+      <c r="C307" s="7"/>
+      <c r="D307" s="7"/>
+      <c r="E307" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A308" s="87"/>
+      <c r="A308" s="85"/>
       <c r="B308" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="C308" s="8"/>
-      <c r="D308" s="8"/>
-      <c r="E308" s="8"/>
+        <v>343</v>
+      </c>
+      <c r="C308" s="7"/>
+      <c r="D308" s="7"/>
+      <c r="E308" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A309" s="87"/>
+      <c r="A309" s="85"/>
       <c r="B309" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="C309" s="8"/>
-      <c r="D309" s="8"/>
-      <c r="E309" s="8"/>
+        <v>344</v>
+      </c>
+      <c r="C309" s="7"/>
+      <c r="D309" s="7"/>
+      <c r="E309" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A310" s="87"/>
+      <c r="A310" s="85"/>
       <c r="B310" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="C310" s="8"/>
-      <c r="D310" s="8"/>
-      <c r="E310" s="8"/>
+        <v>345</v>
+      </c>
+      <c r="C310" s="7"/>
+      <c r="D310" s="7"/>
+      <c r="E310" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A311" s="88"/>
+      <c r="A311" s="86"/>
       <c r="B311" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C311" s="8"/>
-      <c r="D311" s="8"/>
-      <c r="E311" s="8"/>
+        <v>346</v>
+      </c>
+      <c r="C311" s="7"/>
+      <c r="D311" s="7"/>
+      <c r="E311" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A312" s="134" t="s">
-        <v>346</v>
+      <c r="A312" s="132" t="s">
+        <v>347</v>
       </c>
       <c r="B312" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="C312" s="8"/>
-      <c r="D312" s="8"/>
-      <c r="E312" s="8"/>
+        <v>348</v>
+      </c>
+      <c r="C312" s="7"/>
+      <c r="D312" s="7"/>
+      <c r="E312" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A313" s="135"/>
+      <c r="A313" s="133"/>
       <c r="B313" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="C313" s="8"/>
-      <c r="D313" s="8"/>
-      <c r="E313" s="8"/>
+        <v>349</v>
+      </c>
+      <c r="C313" s="7"/>
+      <c r="D313" s="7"/>
+      <c r="E313" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A314" s="135"/>
+      <c r="A314" s="133"/>
       <c r="B314" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C314" s="8"/>
-      <c r="D314" s="8"/>
-      <c r="E314" s="8"/>
+        <v>350</v>
+      </c>
+      <c r="C314" s="7"/>
+      <c r="D314" s="7"/>
+      <c r="E314" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A315" s="135"/>
+      <c r="A315" s="133"/>
       <c r="B315" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="C315" s="8"/>
-      <c r="D315" s="8"/>
-      <c r="E315" s="8"/>
+        <v>351</v>
+      </c>
+      <c r="C315" s="7"/>
+      <c r="D315" s="7"/>
+      <c r="E315" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A316" s="135"/>
+      <c r="A316" s="133"/>
       <c r="B316" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="C316" s="8"/>
-      <c r="D316" s="8"/>
-      <c r="E316" s="8"/>
+        <v>352</v>
+      </c>
+      <c r="C316" s="7"/>
+      <c r="D316" s="7"/>
+      <c r="E316" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A317" s="136"/>
+      <c r="A317" s="134"/>
       <c r="B317" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="C317" s="8"/>
-      <c r="D317" s="8"/>
-      <c r="E317" s="8"/>
+        <v>353</v>
+      </c>
+      <c r="C317" s="7"/>
+      <c r="D317" s="7"/>
+      <c r="E317" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A318" s="137"/>
+      <c r="A318" s="135"/>
       <c r="B318" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="C318" s="8"/>
-      <c r="D318" s="8"/>
-      <c r="E318" s="8"/>
+        <v>354</v>
+      </c>
+      <c r="C318" s="7"/>
+      <c r="D318" s="7"/>
+      <c r="E318" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A319" s="138"/>
+      <c r="A319" s="136"/>
       <c r="B319" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="C319" s="8"/>
-      <c r="D319" s="8"/>
-      <c r="E319" s="8"/>
+        <v>355</v>
+      </c>
+      <c r="C319" s="7"/>
+      <c r="D319" s="7"/>
+      <c r="E319" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A320" s="138"/>
+      <c r="A320" s="136"/>
       <c r="B320" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="C320" s="8"/>
-      <c r="D320" s="8"/>
-      <c r="E320" s="8"/>
+        <v>356</v>
+      </c>
+      <c r="C320" s="7"/>
+      <c r="D320" s="7"/>
+      <c r="E320" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A321" s="138"/>
+      <c r="A321" s="136"/>
       <c r="B321" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C321" s="8"/>
-      <c r="D321" s="8"/>
-      <c r="E321" s="8"/>
+        <v>357</v>
+      </c>
+      <c r="C321" s="7"/>
+      <c r="D321" s="7"/>
+      <c r="E321" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A322" s="138"/>
+      <c r="A322" s="136"/>
       <c r="B322" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="C322" s="8"/>
-      <c r="D322" s="8"/>
-      <c r="E322" s="8"/>
+        <v>358</v>
+      </c>
+      <c r="C322" s="7"/>
+      <c r="D322" s="7"/>
+      <c r="E322" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A323" s="138"/>
+      <c r="A323" s="136"/>
       <c r="B323" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C323" s="8"/>
-      <c r="D323" s="8"/>
-      <c r="E323" s="8"/>
+        <v>359</v>
+      </c>
+      <c r="C323" s="7"/>
+      <c r="D323" s="7"/>
+      <c r="E323" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A324" s="139" t="s">
-        <v>359</v>
+      <c r="A324" s="137" t="s">
+        <v>360</v>
       </c>
       <c r="B324" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="C324" s="8"/>
-      <c r="D324" s="8"/>
-      <c r="E324" s="8"/>
+        <v>361</v>
+      </c>
+      <c r="C324" s="7"/>
+      <c r="D324" s="7"/>
+      <c r="E324" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A325" s="140"/>
+      <c r="A325" s="138"/>
       <c r="B325" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="C325" s="8"/>
-      <c r="D325" s="8"/>
-      <c r="E325" s="8"/>
+        <v>362</v>
+      </c>
+      <c r="C325" s="7"/>
+      <c r="D325" s="7"/>
+      <c r="E325" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A326" s="141"/>
+      <c r="A326" s="139"/>
       <c r="B326" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="C326" s="8"/>
-      <c r="D326" s="8"/>
-      <c r="E326" s="8"/>
+        <v>363</v>
+      </c>
+      <c r="C326" s="7"/>
+      <c r="D326" s="7"/>
+      <c r="E326" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A327" s="8"/>
-      <c r="B327" s="8"/>
-      <c r="C327" s="8"/>
-      <c r="D327" s="8"/>
-      <c r="E327" s="8"/>
+      <c r="A327" s="7"/>
+      <c r="B327" s="7"/>
+      <c r="C327" s="7"/>
+      <c r="D327" s="7"/>
+      <c r="E327" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A328" s="2" t="s">
@@ -10138,232 +10141,232 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A329" s="142" t="s">
-        <v>363</v>
+      <c r="A329" s="140" t="s">
+        <v>364</v>
       </c>
       <c r="B329" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="C329" s="8"/>
-      <c r="D329" s="8"/>
-      <c r="E329" s="8"/>
+        <v>365</v>
+      </c>
+      <c r="C329" s="7"/>
+      <c r="D329" s="7"/>
+      <c r="E329" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A330" s="143"/>
+      <c r="A330" s="141"/>
       <c r="B330" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="C330" s="8"/>
-      <c r="D330" s="8"/>
-      <c r="E330" s="8"/>
+        <v>366</v>
+      </c>
+      <c r="C330" s="7"/>
+      <c r="D330" s="7"/>
+      <c r="E330" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A331" s="143"/>
+      <c r="A331" s="141"/>
       <c r="B331" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="C331" s="8"/>
-      <c r="D331" s="8"/>
-      <c r="E331" s="8"/>
+        <v>367</v>
+      </c>
+      <c r="C331" s="7"/>
+      <c r="D331" s="7"/>
+      <c r="E331" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A332" s="144"/>
+      <c r="A332" s="142"/>
       <c r="B332" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C332" s="8"/>
-      <c r="D332" s="8"/>
-      <c r="E332" s="8"/>
+        <v>368</v>
+      </c>
+      <c r="C332" s="7"/>
+      <c r="D332" s="7"/>
+      <c r="E332" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A333" s="145"/>
-      <c r="B333" s="146" t="s">
-        <v>368</v>
-      </c>
-      <c r="C333" s="145"/>
-      <c r="D333" s="145"/>
-      <c r="E333" s="145"/>
+      <c r="A333" s="143"/>
+      <c r="B333" s="144" t="s">
+        <v>369</v>
+      </c>
+      <c r="C333" s="143"/>
+      <c r="D333" s="143"/>
+      <c r="E333" s="143"/>
     </row>
     <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A334" s="147" t="s">
-        <v>154</v>
+      <c r="A334" s="145" t="s">
+        <v>155</v>
       </c>
       <c r="B334" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="C334" s="8"/>
-      <c r="D334" s="8"/>
-      <c r="E334" s="8"/>
+        <v>370</v>
+      </c>
+      <c r="C334" s="7"/>
+      <c r="D334" s="7"/>
+      <c r="E334" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A335" s="148"/>
+      <c r="A335" s="146"/>
       <c r="B335" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="C335" s="8"/>
-      <c r="D335" s="8"/>
-      <c r="E335" s="8"/>
+        <v>371</v>
+      </c>
+      <c r="C335" s="7"/>
+      <c r="D335" s="7"/>
+      <c r="E335" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A336" s="149" t="s">
-        <v>371</v>
+      <c r="A336" s="147" t="s">
+        <v>372</v>
       </c>
       <c r="B336" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="C336" s="8"/>
-      <c r="D336" s="8"/>
-      <c r="E336" s="8"/>
+        <v>373</v>
+      </c>
+      <c r="C336" s="7"/>
+      <c r="D336" s="7"/>
+      <c r="E336" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A337" s="150"/>
+      <c r="A337" s="148"/>
       <c r="B337" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="C337" s="8"/>
-      <c r="D337" s="8"/>
-      <c r="E337" s="8"/>
+        <v>374</v>
+      </c>
+      <c r="C337" s="7"/>
+      <c r="D337" s="7"/>
+      <c r="E337" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A338" s="150"/>
+      <c r="A338" s="148"/>
       <c r="B338" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="C338" s="8"/>
-      <c r="D338" s="8"/>
-      <c r="E338" s="8"/>
+        <v>375</v>
+      </c>
+      <c r="C338" s="7"/>
+      <c r="D338" s="7"/>
+      <c r="E338" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A339" s="151"/>
+      <c r="A339" s="149"/>
       <c r="B339" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="C339" s="8"/>
-      <c r="D339" s="8"/>
-      <c r="E339" s="8"/>
+        <v>376</v>
+      </c>
+      <c r="C339" s="7"/>
+      <c r="D339" s="7"/>
+      <c r="E339" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="30" customFormat="1" s="1">
       <c r="A340" s="4"/>
       <c r="B340" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C340" s="4"/>
       <c r="D340" s="4"/>
       <c r="E340" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="32.25" customFormat="1" s="1">
-      <c r="A341" s="142" t="s">
-        <v>377</v>
+      <c r="A341" s="140" t="s">
+        <v>378</v>
       </c>
       <c r="B341" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="C341" s="8"/>
-      <c r="D341" s="8"/>
-      <c r="E341" s="8"/>
+        <v>379</v>
+      </c>
+      <c r="C341" s="7"/>
+      <c r="D341" s="7"/>
+      <c r="E341" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="32.25" customFormat="1" s="1">
-      <c r="A342" s="143"/>
-      <c r="B342" s="131" t="s">
-        <v>379</v>
-      </c>
-      <c r="C342" s="132"/>
-      <c r="D342" s="133"/>
-      <c r="E342" s="8"/>
+      <c r="A342" s="141"/>
+      <c r="B342" s="129" t="s">
+        <v>380</v>
+      </c>
+      <c r="C342" s="130"/>
+      <c r="D342" s="131"/>
+      <c r="E342" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="32.25" customFormat="1" s="1">
-      <c r="A343" s="144"/>
+      <c r="A343" s="142"/>
       <c r="B343" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="C343" s="8"/>
-      <c r="D343" s="8"/>
-      <c r="E343" s="8"/>
+        <v>381</v>
+      </c>
+      <c r="C343" s="7"/>
+      <c r="D343" s="7"/>
+      <c r="E343" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A344" s="30" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B344" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="C344" s="8"/>
-      <c r="D344" s="8"/>
-      <c r="E344" s="8"/>
+        <v>383</v>
+      </c>
+      <c r="C344" s="7"/>
+      <c r="D344" s="7"/>
+      <c r="E344" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A345" s="31"/>
       <c r="B345" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="C345" s="8"/>
-      <c r="D345" s="8"/>
-      <c r="E345" s="8"/>
+        <v>384</v>
+      </c>
+      <c r="C345" s="7"/>
+      <c r="D345" s="7"/>
+      <c r="E345" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A346" s="31"/>
       <c r="B346" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="C346" s="8"/>
-      <c r="D346" s="8"/>
-      <c r="E346" s="8"/>
+        <v>385</v>
+      </c>
+      <c r="C346" s="7"/>
+      <c r="D346" s="7"/>
+      <c r="E346" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A347" s="31"/>
       <c r="B347" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="C347" s="8"/>
-      <c r="D347" s="8"/>
-      <c r="E347" s="8"/>
+        <v>386</v>
+      </c>
+      <c r="C347" s="7"/>
+      <c r="D347" s="7"/>
+      <c r="E347" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="16.5" customFormat="1" s="1">
       <c r="A348" s="33"/>
       <c r="B348" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="C348" s="8"/>
-      <c r="D348" s="8"/>
-      <c r="E348" s="8"/>
+        <v>387</v>
+      </c>
+      <c r="C348" s="7"/>
+      <c r="D348" s="7"/>
+      <c r="E348" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="30" customFormat="1" s="1">
       <c r="A349" s="4"/>
       <c r="B349" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C349" s="4"/>
       <c r="D349" s="4"/>
       <c r="E349" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A350" s="152" t="s">
-        <v>388</v>
+      <c r="A350" s="150" t="s">
+        <v>389</v>
       </c>
       <c r="B350" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="C350" s="8"/>
-      <c r="D350" s="8"/>
-      <c r="E350" s="8"/>
+        <v>390</v>
+      </c>
+      <c r="C350" s="7"/>
+      <c r="D350" s="7"/>
+      <c r="E350" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A351" s="153"/>
+      <c r="A351" s="151"/>
       <c r="B351" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="C351" s="8"/>
-      <c r="D351" s="8"/>
-      <c r="E351" s="8"/>
+        <v>391</v>
+      </c>
+      <c r="C351" s="7"/>
+      <c r="D351" s="7"/>
+      <c r="E351" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A352" s="154"/>
+      <c r="A352" s="152"/>
       <c r="B352" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C352" s="8"/>
-      <c r="D352" s="8"/>
-      <c r="E352" s="8"/>
+        <v>392</v>
+      </c>
+      <c r="C352" s="7"/>
+      <c r="D352" s="7"/>
+      <c r="E352" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="57">

--- a/DSA Checklist TUF+.xlsx
+++ b/DSA Checklist TUF+.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="386">
   <si>
     <r>
       <t/>
@@ -170,141 +170,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Rearrange array elements by sign</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Print the matrix in spiral manner</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pascal's Triangle I</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pascal's Triangle II</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pascal's Triangle III</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Rotate matrix by 90 degrees</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Two Sum</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3 Sum</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4 Sum</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Sort an array of 0's 1's and 2's</t>
     </r>
   </si>
@@ -444,6 +309,9 @@
     </r>
   </si>
   <si>
+    <t>Max points on a line</t>
+  </si>
+  <si>
     <r>
       <t/>
     </r>
@@ -502,6 +370,9 @@
       </rPr>
       <t>Count subarrays with given sum</t>
     </r>
+  </si>
+  <si>
+    <t>Count subarrays with sum divisible by k</t>
   </si>
   <si>
     <r>
@@ -6259,7 +6130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="160">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6270,12 +6141,18 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6300,6 +6177,12 @@
     <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6651,7 +6534,7 @@
     <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="15" applyFont="1" fillId="19" applyFill="1" applyAlignment="1">
@@ -6693,6 +6576,9 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="21" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="21" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6718,6 +6604,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7022,14 +6911,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E352"/>
+  <dimension ref="A1:E345"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="153" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="153" width="61.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="153" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="153" width="17.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="153" width="8.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="158" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="158" width="61.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="158" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="159" width="17.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="158" width="8.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
@@ -7042,3391 +6931,3412 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="30.75" customFormat="1" s="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="30" customFormat="1" s="1">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A3" s="6" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="10">
         <v>1</v>
       </c>
-      <c r="E3" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A4" s="9"/>
-      <c r="B4" s="7" t="s">
+      <c r="E3" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A4" s="11"/>
+      <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="10">
         <v>1</v>
       </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A5" s="9"/>
-      <c r="B5" s="7" t="s">
+      <c r="E4" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A5" s="11"/>
+      <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="10">
         <v>1</v>
       </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="7" t="s">
+      <c r="E5" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A6" s="11"/>
+      <c r="B6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="7" t="s">
+      <c r="C6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A7" s="12"/>
+      <c r="B7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="7" t="s">
+      <c r="C7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A9" s="9"/>
-      <c r="B9" s="7" t="s">
+      <c r="B8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A10" s="9"/>
-      <c r="B10" s="7" t="s">
+      <c r="C8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A9" s="14"/>
+      <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A11" s="9"/>
-      <c r="B11" s="7" t="s">
+      <c r="C9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A10" s="14"/>
+      <c r="B10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A12" s="9"/>
-      <c r="B12" s="7" t="s">
+      <c r="C10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A11" s="14"/>
+      <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A13" s="9"/>
-      <c r="B13" s="7" t="s">
+      <c r="C11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A12" s="14"/>
+      <c r="B12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A14" s="9"/>
-      <c r="B14" s="7" t="s">
+      <c r="C12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A13" s="15"/>
+      <c r="B13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A15" s="9"/>
-      <c r="B15" s="7" t="s">
+      <c r="C13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="7" t="s">
+      <c r="C14" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="17">
+        <v>2</v>
+      </c>
+      <c r="E14" s="16"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A15" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A17" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A16" s="19"/>
+      <c r="B16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A18" s="12"/>
-      <c r="B18" s="7" t="s">
+      <c r="C16" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A17" s="19"/>
+      <c r="B17" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A19" s="12"/>
-      <c r="B19" s="7" t="s">
+      <c r="C17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A20" s="12"/>
-      <c r="B20" s="7" t="s">
+      <c r="C18" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="17">
+        <v>2</v>
+      </c>
+      <c r="E18" s="16"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A19" s="20"/>
+      <c r="B19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="7"/>
+      <c r="C19" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="30" customFormat="1" s="1">
+      <c r="A20" s="5"/>
+      <c r="B20" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="5"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A22" s="13"/>
-      <c r="B22" s="7" t="s">
+      <c r="E20" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A21" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A23" s="14" t="s">
+      <c r="B21" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="C21" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="10">
+        <v>1</v>
+      </c>
+      <c r="E21" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A22" s="23"/>
+      <c r="B22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A24" s="15"/>
-      <c r="B24" s="7" t="s">
+      <c r="C22" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="10">
+        <v>1</v>
+      </c>
+      <c r="E22" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A23" s="23"/>
+      <c r="B23" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A25" s="15"/>
-      <c r="B25" s="7" t="s">
+      <c r="C23" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="10">
+        <v>1</v>
+      </c>
+      <c r="E23" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A24" s="23"/>
+      <c r="B24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A26" s="16"/>
-      <c r="B26" s="7" t="s">
+      <c r="C24" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="10">
+        <v>1</v>
+      </c>
+      <c r="E24" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A25" s="23"/>
+      <c r="B25" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="30.75" customFormat="1" s="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="17" t="s">
+      <c r="C25" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="10">
+        <v>1</v>
+      </c>
+      <c r="E25" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A26" s="23"/>
+      <c r="B26" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A28" s="18" t="s">
+      <c r="C26" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="10">
+        <v>1</v>
+      </c>
+      <c r="E26" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A27" s="23"/>
+      <c r="B27" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="C27" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="10">
+        <v>1</v>
+      </c>
+      <c r="E27" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A28" s="23"/>
+      <c r="B28" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A29" s="19"/>
-      <c r="B29" s="7" t="s">
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A29" s="23"/>
+      <c r="B29" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A30" s="19"/>
-      <c r="B30" s="7" t="s">
+      <c r="C29" s="9"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20.25" customFormat="1" s="1">
+      <c r="A30" s="23"/>
+      <c r="B30" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A31" s="19"/>
-      <c r="B31" s="7" t="s">
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A31" s="23"/>
+      <c r="B31" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A32" s="19"/>
-      <c r="B32" s="7" t="s">
+      <c r="C31" s="9"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A32" s="23"/>
+      <c r="B32" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A33" s="19"/>
-      <c r="B33" s="7" t="s">
+      <c r="C32" s="9"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A33" s="23"/>
+      <c r="B33" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A34" s="19"/>
-      <c r="B34" s="7" t="s">
+      <c r="C33" s="9"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A34" s="23"/>
+      <c r="B34" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A35" s="19"/>
-      <c r="B35" s="7" t="s">
+      <c r="C34" s="9"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A35" s="23"/>
+      <c r="B35" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A36" s="19"/>
-      <c r="B36" s="7" t="s">
+      <c r="C35" s="9"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A36" s="23"/>
+      <c r="B36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A37" s="19"/>
-      <c r="B37" s="7" t="s">
+      <c r="A37" s="23"/>
+      <c r="B37" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A38" s="19"/>
-      <c r="B38" s="7" t="s">
+      <c r="A38" s="23"/>
+      <c r="B38" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A39" s="19"/>
-      <c r="B39" s="7" t="s">
+      <c r="A39" s="24"/>
+      <c r="B39" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A40" s="19"/>
-      <c r="B40" s="7" t="s">
+      <c r="A40" s="25"/>
+      <c r="B40" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A41" s="19"/>
-      <c r="B41" s="7" t="s">
+      <c r="A41" s="25"/>
+      <c r="B41" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A42" s="19"/>
-      <c r="B42" s="7" t="s">
+      <c r="A42" s="25"/>
+      <c r="B42" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A43" s="19"/>
-      <c r="B43" s="7" t="s">
+      <c r="A43" s="25"/>
+      <c r="B43" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A44" s="25"/>
+      <c r="B44" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A44" s="19"/>
-      <c r="B44" s="7" t="s">
+      <c r="C44" s="9"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A45" s="25"/>
+      <c r="B45" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A45" s="19"/>
-      <c r="B45" s="7" t="s">
+      <c r="C45" s="9"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A46" s="25"/>
+      <c r="B46" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A46" s="20"/>
-      <c r="B46" s="7" t="s">
+      <c r="C46" s="9"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A47" s="25"/>
+      <c r="B47" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A47" s="21"/>
-      <c r="B47" s="7" t="s">
+      <c r="C47" s="9"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A48" s="26"/>
+      <c r="B48" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A48" s="21"/>
-      <c r="B48" s="7" t="s">
+      <c r="C48" s="9"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A49" s="27"/>
+      <c r="B49" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A49" s="21"/>
-      <c r="B49" s="7" t="s">
+      <c r="C49" s="9"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A50" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A50" s="21"/>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A51" s="29"/>
+      <c r="B51" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="9"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A52" s="29"/>
+      <c r="B52" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" s="9"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A53" s="29"/>
+      <c r="B53" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="9"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A54" s="29"/>
+      <c r="B54" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A55" s="29"/>
+      <c r="B55" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" s="9"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A56" s="29"/>
+      <c r="B56" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="9"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A57" s="29"/>
+      <c r="B57" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="9"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A58" s="29"/>
+      <c r="B58" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A59" s="29"/>
+      <c r="B59" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="9"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A60" s="29"/>
+      <c r="B60" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A61" s="29"/>
+      <c r="B61" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A62" s="29"/>
+      <c r="B62" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="9"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A63" s="29"/>
+      <c r="B63" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="9"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A64" s="29"/>
+      <c r="B64" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" s="9"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A65" s="29"/>
+      <c r="B65" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="9"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A66" s="30"/>
+      <c r="B66" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" s="9"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A67" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C67" s="9"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A68" s="32"/>
+      <c r="B68" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C68" s="9"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A69" s="32"/>
+      <c r="B69" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C69" s="9"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A70" s="32"/>
+      <c r="B70" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70" s="9"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A71" s="32"/>
+      <c r="B71" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" s="9"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A72" s="32"/>
+      <c r="B72" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" s="9"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A73" s="32"/>
+      <c r="B73" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A74" s="32"/>
+      <c r="B74" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="9"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A75" s="32"/>
+      <c r="B75" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" s="9"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A76" s="32"/>
+      <c r="B76" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C76" s="9"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A77" s="32"/>
+      <c r="B77" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" s="9"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A78" s="33"/>
+      <c r="B78" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C78" s="9"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A79" s="34"/>
+      <c r="B79" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C79" s="9"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A80" s="35"/>
+      <c r="B80" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A81" s="35"/>
+      <c r="B81" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A82" s="35"/>
+      <c r="B82" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A83" s="35"/>
+      <c r="B83" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A84" s="35"/>
+      <c r="B84" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" s="9"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A85" s="35"/>
+      <c r="B85" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" s="9"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A86" s="36"/>
+      <c r="B86" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C86" s="9"/>
+      <c r="D86" s="10"/>
+      <c r="E86" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A87" s="35"/>
+      <c r="B87" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C87" s="9"/>
+      <c r="D87" s="10"/>
+      <c r="E87" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A88" s="37"/>
+      <c r="B88" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A89" s="38"/>
+      <c r="B89" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C89" s="9"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A90" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D90" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E90" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A51" s="21"/>
-      <c r="B51" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A52" s="21"/>
-      <c r="B52" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A53" s="21"/>
-      <c r="B53" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A54" s="21"/>
-      <c r="B54" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A55" s="22"/>
-      <c r="B55" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A56" s="23"/>
-      <c r="B56" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A57" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A58" s="25"/>
-      <c r="B58" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A59" s="25"/>
-      <c r="B59" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A60" s="25"/>
-      <c r="B60" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A61" s="25"/>
-      <c r="B61" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A62" s="25"/>
-      <c r="B62" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A63" s="25"/>
-      <c r="B63" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A64" s="25"/>
-      <c r="B64" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A65" s="25"/>
-      <c r="B65" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A66" s="25"/>
-      <c r="B66" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A67" s="25"/>
-      <c r="B67" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A68" s="25"/>
-      <c r="B68" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A69" s="25"/>
-      <c r="B69" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A70" s="25"/>
-      <c r="B70" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A71" s="25"/>
-      <c r="B71" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A72" s="25"/>
-      <c r="B72" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A73" s="26"/>
-      <c r="B73" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A74" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A75" s="28"/>
-      <c r="B75" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A76" s="28"/>
-      <c r="B76" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A77" s="28"/>
-      <c r="B77" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A78" s="28"/>
-      <c r="B78" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A79" s="28"/>
-      <c r="B79" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A80" s="28"/>
-      <c r="B80" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A81" s="28"/>
-      <c r="B81" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A82" s="28"/>
-      <c r="B82" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A83" s="28"/>
-      <c r="B83" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A84" s="28"/>
-      <c r="B84" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A85" s="29"/>
-      <c r="B85" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A86" s="30"/>
-      <c r="B86" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A87" s="31"/>
-      <c r="B87" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A88" s="31"/>
-      <c r="B88" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A89" s="31"/>
-      <c r="B89" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A90" s="31"/>
-      <c r="B90" s="7" t="s">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A91" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A91" s="31"/>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="10"/>
+      <c r="E91" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A92" s="31"/>
-      <c r="B92" s="7" t="s">
+      <c r="A92" s="40"/>
+      <c r="B92" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A93" s="32"/>
-      <c r="B93" s="7" t="s">
+      <c r="A93" s="40"/>
+      <c r="B93" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="10"/>
+      <c r="E93" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A94" s="31"/>
-      <c r="B94" s="7" t="s">
+      <c r="A94" s="40"/>
+      <c r="B94" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A95" s="33"/>
-      <c r="B95" s="7" t="s">
+      <c r="A95" s="41"/>
+      <c r="B95" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="10"/>
+      <c r="E95" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A96" s="34"/>
-      <c r="B96" s="7" t="s">
+      <c r="A96" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
+      <c r="B96" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96" s="9"/>
+      <c r="D96" s="10"/>
+      <c r="E96" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="43"/>
+      <c r="B97" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C97" s="9"/>
+      <c r="D97" s="10"/>
+      <c r="E97" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A98" s="43"/>
+      <c r="B98" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C98" s="9"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A99" s="43"/>
+      <c r="B99" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="10"/>
+      <c r="E99" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A100" s="43"/>
+      <c r="B100" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C100" s="9"/>
+      <c r="D100" s="10"/>
+      <c r="E100" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A101" s="43"/>
+      <c r="B101" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C101" s="9"/>
+      <c r="D101" s="10"/>
+      <c r="E101" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A102" s="43"/>
+      <c r="B102" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C102" s="9"/>
+      <c r="D102" s="10"/>
+      <c r="E102" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A103" s="44"/>
+      <c r="B103" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C103" s="9"/>
+      <c r="D103" s="10"/>
+      <c r="E103" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A104" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C104" s="9"/>
+      <c r="D104" s="10"/>
+      <c r="E104" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A105" s="46"/>
+      <c r="B105" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C105" s="9"/>
+      <c r="D105" s="10"/>
+      <c r="E105" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A106" s="46"/>
+      <c r="B106" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C106" s="9"/>
+      <c r="D106" s="10"/>
+      <c r="E106" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A107" s="46"/>
+      <c r="B107" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C107" s="9"/>
+      <c r="D107" s="10"/>
+      <c r="E107" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A108" s="46"/>
+      <c r="B108" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C108" s="9"/>
+      <c r="D108" s="10"/>
+      <c r="E108" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A109" s="47"/>
+      <c r="B109" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" s="9"/>
+      <c r="D109" s="10"/>
+      <c r="E109" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A110" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C110" s="9"/>
+      <c r="D110" s="10"/>
+      <c r="E110" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A111" s="37"/>
+      <c r="B111" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C111" s="9"/>
+      <c r="D111" s="10"/>
+      <c r="E111" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A112" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C112" s="9"/>
+      <c r="D112" s="10"/>
+      <c r="E112" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A113" s="49"/>
+      <c r="B113" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C113" s="9"/>
+      <c r="D113" s="10"/>
+      <c r="E113" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A114" s="49"/>
+      <c r="B114" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C114" s="9"/>
+      <c r="D114" s="10"/>
+      <c r="E114" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A115" s="49"/>
+      <c r="B115" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C115" s="9"/>
+      <c r="D115" s="10"/>
+      <c r="E115" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A116" s="49"/>
+      <c r="B116" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C116" s="9"/>
+      <c r="D116" s="10"/>
+      <c r="E116" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A117" s="49"/>
+      <c r="B117" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C117" s="9"/>
+      <c r="D117" s="10"/>
+      <c r="E117" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A118" s="49"/>
+      <c r="B118" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C118" s="9"/>
+      <c r="D118" s="10"/>
+      <c r="E118" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A119" s="50"/>
+      <c r="B119" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C119" s="9"/>
+      <c r="D119" s="10"/>
+      <c r="E119" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A120" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C120" s="9"/>
+      <c r="D120" s="10"/>
+      <c r="E120" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A121" s="52"/>
+      <c r="B121" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C121" s="9"/>
+      <c r="D121" s="10"/>
+      <c r="E121" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A122" s="53"/>
+      <c r="B122" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C122" s="9"/>
+      <c r="D122" s="10"/>
+      <c r="E122" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A123" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C123" s="9"/>
+      <c r="D123" s="10"/>
+      <c r="E123" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A124" s="55"/>
+      <c r="B124" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C124" s="9"/>
+      <c r="D124" s="10"/>
+      <c r="E124" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A125" s="55"/>
+      <c r="B125" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C125" s="9"/>
+      <c r="D125" s="10"/>
+      <c r="E125" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A126" s="55"/>
+      <c r="B126" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C126" s="9"/>
+      <c r="D126" s="10"/>
+      <c r="E126" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A127" s="55"/>
+      <c r="B127" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C127" s="9"/>
+      <c r="D127" s="10"/>
+      <c r="E127" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A128" s="56"/>
+      <c r="B128" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C128" s="9"/>
+      <c r="D128" s="10"/>
+      <c r="E128" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A129" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C129" s="9"/>
+      <c r="D129" s="10"/>
+      <c r="E129" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A130" s="58"/>
+      <c r="B130" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C130" s="9"/>
+      <c r="D130" s="10"/>
+      <c r="E130" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A131" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C131" s="9"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A132" s="60"/>
+      <c r="B132" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C132" s="9"/>
+      <c r="D132" s="10"/>
+      <c r="E132" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A133" s="61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C133" s="9"/>
+      <c r="D133" s="10"/>
+      <c r="E133" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A134" s="60"/>
+      <c r="B134" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C134" s="9"/>
+      <c r="D134" s="10"/>
+      <c r="E134" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A135" s="60"/>
+      <c r="B135" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C135" s="9"/>
+      <c r="D135" s="10"/>
+      <c r="E135" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A136" s="62"/>
+      <c r="B136" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C136" s="9"/>
+      <c r="D136" s="10"/>
+      <c r="E136" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A137" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B137" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C137" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D137" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E137" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A98" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A99" s="36"/>
-      <c r="B99" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A100" s="36"/>
-      <c r="B100" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A101" s="36"/>
-      <c r="B101" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A102" s="37"/>
-      <c r="B102" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A103" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A104" s="39"/>
-      <c r="B104" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A105" s="39"/>
-      <c r="B105" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A106" s="39"/>
-      <c r="B106" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A107" s="39"/>
-      <c r="B107" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A108" s="39"/>
-      <c r="B108" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A109" s="39"/>
-      <c r="B109" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A110" s="40"/>
-      <c r="B110" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A111" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C111" s="7"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A112" s="42"/>
-      <c r="B112" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A113" s="42"/>
-      <c r="B113" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A114" s="42"/>
-      <c r="B114" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A115" s="42"/>
-      <c r="B115" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A116" s="43"/>
-      <c r="B116" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A117" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A118" s="33"/>
-      <c r="B118" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A119" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C119" s="7"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A120" s="45"/>
-      <c r="B120" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A121" s="45"/>
-      <c r="B121" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A122" s="45"/>
-      <c r="B122" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A123" s="45"/>
-      <c r="B123" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A124" s="45"/>
-      <c r="B124" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A125" s="45"/>
-      <c r="B125" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A126" s="46"/>
-      <c r="B126" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A127" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A128" s="48"/>
-      <c r="B128" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A129" s="49"/>
-      <c r="B129" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A130" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A131" s="51"/>
-      <c r="B131" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A132" s="51"/>
-      <c r="B132" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A133" s="51"/>
-      <c r="B133" s="7" t="s">
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A138" s="63" t="s">
+        <v>155</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C138" s="9"/>
+      <c r="D138" s="10"/>
+      <c r="E138" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A139" s="64"/>
+      <c r="B139" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C139" s="9"/>
+      <c r="D139" s="10"/>
+      <c r="E139" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A140" s="64"/>
+      <c r="B140" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C140" s="9"/>
+      <c r="D140" s="10"/>
+      <c r="E140" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A141" s="64"/>
+      <c r="B141" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C141" s="9"/>
+      <c r="D141" s="10"/>
+      <c r="E141" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A142" s="65"/>
+      <c r="B142" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C142" s="9"/>
+      <c r="D142" s="10"/>
+      <c r="E142" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A143" s="66" t="s">
+        <v>161</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C143" s="9"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A144" s="67"/>
+      <c r="B144" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C144" s="9"/>
+      <c r="D144" s="10"/>
+      <c r="E144" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A145" s="67"/>
+      <c r="B145" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C145" s="9"/>
+      <c r="D145" s="10"/>
+      <c r="E145" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A146" s="67"/>
+      <c r="B146" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C146" s="9"/>
+      <c r="D146" s="10"/>
+      <c r="E146" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A147" s="67"/>
+      <c r="B147" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C147" s="9"/>
+      <c r="D147" s="10"/>
+      <c r="E147" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A148" s="67"/>
+      <c r="B148" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C148" s="9"/>
+      <c r="D148" s="10"/>
+      <c r="E148" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A149" s="67"/>
+      <c r="B149" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C149" s="9"/>
+      <c r="D149" s="10"/>
+      <c r="E149" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A150" s="68"/>
+      <c r="B150" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C150" s="9"/>
+      <c r="D150" s="10"/>
+      <c r="E150" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A151" s="69" t="s">
+        <v>170</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C151" s="9"/>
+      <c r="D151" s="10"/>
+      <c r="E151" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A152" s="70"/>
+      <c r="B152" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C152" s="9"/>
+      <c r="D152" s="10"/>
+      <c r="E152" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A153" s="70"/>
+      <c r="B153" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C153" s="9"/>
+      <c r="D153" s="10"/>
+      <c r="E153" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A154" s="70"/>
+      <c r="B154" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C154" s="9"/>
+      <c r="D154" s="10"/>
+      <c r="E154" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A155" s="70"/>
+      <c r="B155" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C155" s="9"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A156" s="71"/>
+      <c r="B156" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C156" s="9"/>
+      <c r="D156" s="10"/>
+      <c r="E156" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A157" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C157" s="9"/>
+      <c r="D157" s="10"/>
+      <c r="E157" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A158" s="73"/>
+      <c r="B158" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C158" s="9"/>
+      <c r="D158" s="10"/>
+      <c r="E158" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A159" s="73"/>
+      <c r="B159" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C159" s="9"/>
+      <c r="D159" s="10"/>
+      <c r="E159" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A160" s="73"/>
+      <c r="B160" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C160" s="9"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A161" s="73"/>
+      <c r="B161" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C161" s="9"/>
+      <c r="D161" s="10"/>
+      <c r="E161" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A162" s="73"/>
+      <c r="B162" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C162" s="9"/>
+      <c r="D162" s="10"/>
+      <c r="E162" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A163" s="73"/>
+      <c r="B163" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C163" s="9"/>
+      <c r="D163" s="10"/>
+      <c r="E163" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A164" s="73"/>
+      <c r="B164" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C164" s="9"/>
+      <c r="D164" s="10"/>
+      <c r="E164" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A165" s="74"/>
+      <c r="B165" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C165" s="9"/>
+      <c r="D165" s="10"/>
+      <c r="E165" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A166" s="75" t="s">
+        <v>187</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C166" s="9"/>
+      <c r="D166" s="10"/>
+      <c r="E166" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A167" s="76"/>
+      <c r="B167" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C167" s="9"/>
+      <c r="D167" s="10"/>
+      <c r="E167" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A168" s="76"/>
+      <c r="B168" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C168" s="9"/>
+      <c r="D168" s="10"/>
+      <c r="E168" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A169" s="76"/>
+      <c r="B169" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C169" s="9"/>
+      <c r="D169" s="10"/>
+      <c r="E169" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A170" s="76"/>
+      <c r="B170" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C170" s="9"/>
+      <c r="D170" s="10"/>
+      <c r="E170" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A171" s="77"/>
+      <c r="B171" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C171" s="9"/>
+      <c r="D171" s="10"/>
+      <c r="E171" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A172" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B172" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C172" s="9"/>
+      <c r="D172" s="10"/>
+      <c r="E172" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A173" s="43"/>
+      <c r="B173" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C173" s="9"/>
+      <c r="D173" s="10"/>
+      <c r="E173" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A174" s="43"/>
+      <c r="B174" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C174" s="9"/>
+      <c r="D174" s="10"/>
+      <c r="E174" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A175" s="43"/>
+      <c r="B175" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C175" s="9"/>
+      <c r="D175" s="10"/>
+      <c r="E175" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A176" s="43"/>
+      <c r="B176" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C176" s="9"/>
+      <c r="D176" s="10"/>
+      <c r="E176" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A177" s="44"/>
+      <c r="B177" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C177" s="9"/>
+      <c r="D177" s="10"/>
+      <c r="E177" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A178" s="78" t="s">
+        <v>200</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C178" s="9"/>
+      <c r="D178" s="10"/>
+      <c r="E178" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A179" s="79"/>
+      <c r="B179" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C179" s="9"/>
+      <c r="D179" s="10"/>
+      <c r="E179" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A180" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C180" s="9"/>
+      <c r="D180" s="10"/>
+      <c r="E180" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A181" s="79"/>
+      <c r="B181" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C181" s="9"/>
+      <c r="D181" s="10"/>
+      <c r="E181" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A182" s="79"/>
+      <c r="B182" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C182" s="9"/>
+      <c r="D182" s="10"/>
+      <c r="E182" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A183" s="81"/>
+      <c r="B183" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C183" s="9"/>
+      <c r="D183" s="10"/>
+      <c r="E183" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A184" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A185" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C185" s="9"/>
+      <c r="D185" s="10"/>
+      <c r="E185" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A186" s="79"/>
+      <c r="B186" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C186" s="9"/>
+      <c r="D186" s="10"/>
+      <c r="E186" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A187" s="79"/>
+      <c r="B187" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C187" s="9"/>
+      <c r="D187" s="10"/>
+      <c r="E187" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A188" s="79"/>
+      <c r="B188" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C188" s="9"/>
+      <c r="D188" s="10"/>
+      <c r="E188" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A189" s="79"/>
+      <c r="B189" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C189" s="9"/>
+      <c r="D189" s="10"/>
+      <c r="E189" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A190" s="81"/>
+      <c r="B190" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C190" s="9"/>
+      <c r="D190" s="10"/>
+      <c r="E190" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A191" s="82" t="s">
+        <v>214</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C191" s="9"/>
+      <c r="D191" s="10"/>
+      <c r="E191" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A192" s="83"/>
+      <c r="B192" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C192" s="9"/>
+      <c r="D192" s="10"/>
+      <c r="E192" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A193" s="83"/>
+      <c r="B193" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C193" s="9"/>
+      <c r="D193" s="10"/>
+      <c r="E193" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A194" s="84"/>
+      <c r="B194" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C194" s="9"/>
+      <c r="D194" s="10"/>
+      <c r="E194" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A195" s="66" t="s">
+        <v>219</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C195" s="9"/>
+      <c r="D195" s="10"/>
+      <c r="E195" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A196" s="68"/>
+      <c r="B196" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C196" s="9"/>
+      <c r="D196" s="10"/>
+      <c r="E196" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="30" customFormat="1" s="1">
+      <c r="A197" s="5"/>
+      <c r="B197" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C197" s="5"/>
+      <c r="D197" s="7"/>
+      <c r="E197" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A198" s="85" t="s">
+        <v>223</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C198" s="9"/>
+      <c r="D198" s="10"/>
+      <c r="E198" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A199" s="86"/>
+      <c r="B199" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C199" s="9"/>
+      <c r="D199" s="10"/>
+      <c r="E199" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A200" s="87"/>
+      <c r="B200" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C200" s="9"/>
+      <c r="D200" s="10"/>
+      <c r="E200" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A201" s="88" t="s">
+        <v>227</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C201" s="9"/>
+      <c r="D201" s="10"/>
+      <c r="E201" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A202" s="89"/>
+      <c r="B202" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C202" s="9"/>
+      <c r="D202" s="10"/>
+      <c r="E202" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A203" s="89"/>
+      <c r="B203" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C203" s="9"/>
+      <c r="D203" s="10"/>
+      <c r="E203" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A204" s="89"/>
+      <c r="B204" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C204" s="9"/>
+      <c r="D204" s="10"/>
+      <c r="E204" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A205" s="89"/>
+      <c r="B205" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C205" s="9"/>
+      <c r="D205" s="10"/>
+      <c r="E205" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A206" s="89"/>
+      <c r="B206" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C206" s="9"/>
+      <c r="D206" s="10"/>
+      <c r="E206" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A207" s="90"/>
+      <c r="B207" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C207" s="9"/>
+      <c r="D207" s="10"/>
+      <c r="E207" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A208" s="91" t="s">
+        <v>235</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C208" s="9"/>
+      <c r="D208" s="10"/>
+      <c r="E208" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A209" s="92"/>
+      <c r="B209" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C209" s="9"/>
+      <c r="D209" s="10"/>
+      <c r="E209" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A210" s="92"/>
+      <c r="B210" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C210" s="9"/>
+      <c r="D210" s="10"/>
+      <c r="E210" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A211" s="93"/>
+      <c r="B211" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C211" s="9"/>
+      <c r="D211" s="10"/>
+      <c r="E211" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="30" customFormat="1" s="1">
+      <c r="A212" s="5"/>
+      <c r="B212" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C212" s="5"/>
+      <c r="D212" s="7"/>
+      <c r="E212" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A213" s="94" t="s">
+        <v>241</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C213" s="9"/>
+      <c r="D213" s="10"/>
+      <c r="E213" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A214" s="95"/>
+      <c r="B214" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C214" s="9"/>
+      <c r="D214" s="10"/>
+      <c r="E214" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A215" s="95"/>
+      <c r="B215" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C215" s="9"/>
+      <c r="D215" s="10"/>
+      <c r="E215" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A216" s="95"/>
+      <c r="B216" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C216" s="9"/>
+      <c r="D216" s="10"/>
+      <c r="E216" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A217" s="95"/>
+      <c r="B217" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C217" s="9"/>
+      <c r="D217" s="10"/>
+      <c r="E217" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A218" s="95"/>
+      <c r="B218" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C218" s="9"/>
+      <c r="D218" s="10"/>
+      <c r="E218" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A219" s="95"/>
+      <c r="B219" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C219" s="9"/>
+      <c r="D219" s="10"/>
+      <c r="E219" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A220" s="95"/>
+      <c r="B220" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C220" s="9"/>
+      <c r="D220" s="10"/>
+      <c r="E220" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A221" s="96"/>
+      <c r="B221" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C221" s="9"/>
+      <c r="D221" s="10"/>
+      <c r="E221" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A222" s="97" t="s">
+        <v>251</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="C222" s="9"/>
+      <c r="D222" s="10"/>
+      <c r="E222" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="30" customFormat="1" s="1">
+      <c r="A223" s="5"/>
+      <c r="B223" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C223" s="5"/>
+      <c r="D223" s="7"/>
+      <c r="E223" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A224" s="98" t="s">
+        <v>254</v>
+      </c>
+      <c r="B224" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C224" s="9"/>
+      <c r="D224" s="10"/>
+      <c r="E224" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A225" s="99"/>
+      <c r="B225" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C225" s="9"/>
+      <c r="D225" s="10"/>
+      <c r="E225" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A226" s="100"/>
+      <c r="B226" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C226" s="9"/>
+      <c r="D226" s="10"/>
+      <c r="E226" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="14.5" customFormat="1" s="1">
+      <c r="A227" s="9"/>
+      <c r="B227" s="9"/>
+      <c r="C227" s="9"/>
+      <c r="D227" s="10"/>
+      <c r="E227" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A228" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A229" s="101" t="s">
+        <v>258</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C229" s="9"/>
+      <c r="D229" s="10"/>
+      <c r="E229" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A230" s="102"/>
+      <c r="B230" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C230" s="9"/>
+      <c r="D230" s="10"/>
+      <c r="E230" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A231" s="102"/>
+      <c r="B231" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="C231" s="9"/>
+      <c r="D231" s="10"/>
+      <c r="E231" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A232" s="102"/>
+      <c r="B232" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="C232" s="9"/>
+      <c r="D232" s="10"/>
+      <c r="E232" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A233" s="102"/>
+      <c r="B233" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C233" s="9"/>
+      <c r="D233" s="10"/>
+      <c r="E233" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A234" s="102"/>
+      <c r="B234" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C234" s="9"/>
+      <c r="D234" s="10"/>
+      <c r="E234" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A235" s="102"/>
+      <c r="B235" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C235" s="9"/>
+      <c r="D235" s="10"/>
+      <c r="E235" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A236" s="103"/>
+      <c r="B236" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="C236" s="9"/>
+      <c r="D236" s="10"/>
+      <c r="E236" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A237" s="104" t="s">
+        <v>267</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C237" s="9"/>
+      <c r="D237" s="10"/>
+      <c r="E237" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A238" s="105"/>
+      <c r="B238" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C238" s="9"/>
+      <c r="D238" s="10"/>
+      <c r="E238" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A239" s="105"/>
+      <c r="B239" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C239" s="9"/>
+      <c r="D239" s="10"/>
+      <c r="E239" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A240" s="106"/>
+      <c r="B240" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="C240" s="9"/>
+      <c r="D240" s="10"/>
+      <c r="E240" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A241" s="107" t="s">
+        <v>272</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C241" s="9"/>
+      <c r="D241" s="10"/>
+      <c r="E241" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A242" s="108"/>
+      <c r="B242" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C242" s="9"/>
+      <c r="D242" s="10"/>
+      <c r="E242" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A243" s="108"/>
+      <c r="B243" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C243" s="9"/>
+      <c r="D243" s="10"/>
+      <c r="E243" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A244" s="108"/>
+      <c r="B244" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C244" s="9"/>
+      <c r="D244" s="10"/>
+      <c r="E244" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A245" s="108"/>
+      <c r="B245" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C245" s="9"/>
+      <c r="D245" s="10"/>
+      <c r="E245" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A246" s="108"/>
+      <c r="B246" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C246" s="9"/>
+      <c r="D246" s="10"/>
+      <c r="E246" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A247" s="108"/>
+      <c r="B247" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C247" s="9"/>
+      <c r="D247" s="10"/>
+      <c r="E247" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A248" s="109"/>
+      <c r="B248" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C248" s="9"/>
+      <c r="D248" s="10"/>
+      <c r="E248" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A249" s="110" t="s">
+        <v>281</v>
+      </c>
+      <c r="B249" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C249" s="9"/>
+      <c r="D249" s="10"/>
+      <c r="E249" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A250" s="111"/>
+      <c r="B250" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="C250" s="9"/>
+      <c r="D250" s="10"/>
+      <c r="E250" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A251" s="111"/>
+      <c r="B251" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C251" s="9"/>
+      <c r="D251" s="10"/>
+      <c r="E251" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A252" s="111"/>
+      <c r="B252" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C252" s="9"/>
+      <c r="D252" s="10"/>
+      <c r="E252" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A253" s="111"/>
+      <c r="B253" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C253" s="9"/>
+      <c r="D253" s="10"/>
+      <c r="E253" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A254" s="111"/>
+      <c r="B254" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C254" s="9"/>
+      <c r="D254" s="10"/>
+      <c r="E254" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A255" s="111"/>
+      <c r="B255" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C255" s="9"/>
+      <c r="D255" s="10"/>
+      <c r="E255" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A256" s="111"/>
+      <c r="B256" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C256" s="9"/>
+      <c r="D256" s="10"/>
+      <c r="E256" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A257" s="111"/>
+      <c r="B257" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C257" s="9"/>
+      <c r="D257" s="10"/>
+      <c r="E257" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A258" s="112"/>
+      <c r="B258" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="C258" s="9"/>
+      <c r="D258" s="10"/>
+      <c r="E258" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A259" s="113" t="s">
+        <v>292</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C259" s="9"/>
+      <c r="D259" s="10"/>
+      <c r="E259" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A260" s="114"/>
+      <c r="B260" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C260" s="9"/>
+      <c r="D260" s="10"/>
+      <c r="E260" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A261" s="115"/>
+      <c r="B261" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="C261" s="9"/>
+      <c r="D261" s="10"/>
+      <c r="E261" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A262" s="116" t="s">
+        <v>296</v>
+      </c>
+      <c r="B262" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C262" s="9"/>
+      <c r="D262" s="10"/>
+      <c r="E262" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A263" s="117"/>
+      <c r="B263" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="C263" s="9"/>
+      <c r="D263" s="10"/>
+      <c r="E263" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A264" s="117"/>
+      <c r="B264" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C264" s="9"/>
+      <c r="D264" s="10"/>
+      <c r="E264" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A265" s="117"/>
+      <c r="B265" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="C265" s="9"/>
+      <c r="D265" s="10"/>
+      <c r="E265" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A266" s="118"/>
+      <c r="B266" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="C266" s="9"/>
+      <c r="D266" s="10"/>
+      <c r="E266" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A267" s="119" t="s">
+        <v>302</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C267" s="9"/>
+      <c r="D267" s="10"/>
+      <c r="E267" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A268" s="120"/>
+      <c r="B268" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="C268" s="9"/>
+      <c r="D268" s="10"/>
+      <c r="E268" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A269" s="121"/>
+      <c r="B269" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C269" s="9"/>
+      <c r="D269" s="10"/>
+      <c r="E269" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="14.5" customFormat="1" s="1">
+      <c r="A270" s="9"/>
+      <c r="B270" s="9"/>
+      <c r="C270" s="9"/>
+      <c r="D270" s="10"/>
+      <c r="E270" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="14.5" customFormat="1" s="1">
+      <c r="A271" s="9"/>
+      <c r="B271" s="9"/>
+      <c r="C271" s="9"/>
+      <c r="D271" s="10"/>
+      <c r="E271" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="14.5" customFormat="1" s="1">
+      <c r="A272" s="9"/>
+      <c r="B272" s="9"/>
+      <c r="C272" s="9"/>
+      <c r="D272" s="10"/>
+      <c r="E272" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="14.5" customFormat="1" s="1">
+      <c r="A273" s="9"/>
+      <c r="B273" s="9"/>
+      <c r="C273" s="9"/>
+      <c r="D273" s="10"/>
+      <c r="E273" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="14.5" customFormat="1" s="1">
+      <c r="A274" s="9"/>
+      <c r="B274" s="9"/>
+      <c r="C274" s="9"/>
+      <c r="D274" s="10"/>
+      <c r="E274" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A275" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D275" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="30" customFormat="1" s="1">
+      <c r="A276" s="5"/>
+      <c r="B276" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="C276" s="5"/>
+      <c r="D276" s="7"/>
+      <c r="E276" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A277" s="122" t="s">
+        <v>188</v>
+      </c>
+      <c r="B277" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C277" s="9"/>
+      <c r="D277" s="10"/>
+      <c r="E277" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A278" s="123" t="s">
+        <v>308</v>
+      </c>
+      <c r="B278" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="C278" s="9"/>
+      <c r="D278" s="10"/>
+      <c r="E278" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A279" s="124"/>
+      <c r="B279" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="C279" s="9"/>
+      <c r="D279" s="10"/>
+      <c r="E279" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A280" s="124"/>
+      <c r="B280" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C280" s="9"/>
+      <c r="D280" s="10"/>
+      <c r="E280" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A281" s="124"/>
+      <c r="B281" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C281" s="9"/>
+      <c r="D281" s="10"/>
+      <c r="E281" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A282" s="125"/>
+      <c r="B282" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C282" s="9"/>
+      <c r="D282" s="10"/>
+      <c r="E282" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A283" s="126" t="s">
+        <v>314</v>
+      </c>
+      <c r="B283" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C283" s="9"/>
+      <c r="D283" s="10"/>
+      <c r="E283" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A284" s="127" t="s">
+        <v>316</v>
+      </c>
+      <c r="B284" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C284" s="9"/>
+      <c r="D284" s="10"/>
+      <c r="E284" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A285" s="128"/>
+      <c r="B285" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C285" s="9"/>
+      <c r="D285" s="10"/>
+      <c r="E285" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A286" s="128"/>
+      <c r="B286" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="C286" s="9"/>
+      <c r="D286" s="10"/>
+      <c r="E286" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A287" s="128"/>
+      <c r="B287" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C287" s="9"/>
+      <c r="D287" s="10"/>
+      <c r="E287" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A288" s="129"/>
+      <c r="B288" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C288" s="9"/>
+      <c r="D288" s="10"/>
+      <c r="E288" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A289" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="B289" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C289" s="9"/>
+      <c r="D289" s="10"/>
+      <c r="E289" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A290" s="131"/>
+      <c r="B290" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C290" s="9"/>
+      <c r="D290" s="10"/>
+      <c r="E290" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A291" s="131"/>
+      <c r="B291" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="C291" s="9"/>
+      <c r="D291" s="10"/>
+      <c r="E291" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A292" s="131"/>
+      <c r="B292" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C292" s="9"/>
+      <c r="D292" s="10"/>
+      <c r="E292" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A293" s="132"/>
+      <c r="B293" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C293" s="9"/>
+      <c r="D293" s="10"/>
+      <c r="E293" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A294" s="88" t="s">
+        <v>328</v>
+      </c>
+      <c r="B294" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C294" s="9"/>
+      <c r="D294" s="10"/>
+      <c r="E294" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A295" s="89"/>
+      <c r="B295" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C295" s="9"/>
+      <c r="D295" s="10"/>
+      <c r="E295" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A296" s="89"/>
+      <c r="B296" s="133" t="s">
+        <v>331</v>
+      </c>
+      <c r="C296" s="134"/>
+      <c r="D296" s="135"/>
+      <c r="E296" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A297" s="89"/>
+      <c r="B297" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="C297" s="9"/>
+      <c r="D297" s="10"/>
+      <c r="E297" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A298" s="89"/>
+      <c r="B298" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C298" s="9"/>
+      <c r="D298" s="10"/>
+      <c r="E298" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A299" s="89"/>
+      <c r="B299" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C299" s="9"/>
+      <c r="D299" s="10"/>
+      <c r="E299" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A300" s="89"/>
+      <c r="B300" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C300" s="9"/>
+      <c r="D300" s="10"/>
+      <c r="E300" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A301" s="89"/>
+      <c r="B301" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C301" s="9"/>
+      <c r="D301" s="10"/>
+      <c r="E301" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A302" s="89"/>
+      <c r="B302" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="C302" s="9"/>
+      <c r="D302" s="10"/>
+      <c r="E302" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A303" s="89"/>
+      <c r="B303" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C303" s="9"/>
+      <c r="D303" s="10"/>
+      <c r="E303" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A304" s="90"/>
+      <c r="B304" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C304" s="9"/>
+      <c r="D304" s="10"/>
+      <c r="E304" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A305" s="136" t="s">
+        <v>340</v>
+      </c>
+      <c r="B305" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C305" s="9"/>
+      <c r="D305" s="10"/>
+      <c r="E305" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A306" s="137"/>
+      <c r="B306" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C306" s="9"/>
+      <c r="D306" s="10"/>
+      <c r="E306" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A307" s="137"/>
+      <c r="B307" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="C307" s="9"/>
+      <c r="D307" s="10"/>
+      <c r="E307" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A308" s="137"/>
+      <c r="B308" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="C308" s="9"/>
+      <c r="D308" s="10"/>
+      <c r="E308" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A309" s="137"/>
+      <c r="B309" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C309" s="9"/>
+      <c r="D309" s="10"/>
+      <c r="E309" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A310" s="138"/>
+      <c r="B310" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C310" s="9"/>
+      <c r="D310" s="10"/>
+      <c r="E310" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A311" s="139"/>
+      <c r="B311" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C311" s="9"/>
+      <c r="D311" s="10"/>
+      <c r="E311" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A312" s="140"/>
+      <c r="B312" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="C312" s="9"/>
+      <c r="D312" s="10"/>
+      <c r="E312" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A313" s="140"/>
+      <c r="B313" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C313" s="9"/>
+      <c r="D313" s="10"/>
+      <c r="E313" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A314" s="140"/>
+      <c r="B314" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C314" s="9"/>
+      <c r="D314" s="10"/>
+      <c r="E314" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A315" s="140"/>
+      <c r="B315" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C315" s="9"/>
+      <c r="D315" s="10"/>
+      <c r="E315" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A316" s="140"/>
+      <c r="B316" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="C316" s="9"/>
+      <c r="D316" s="10"/>
+      <c r="E316" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A317" s="141" t="s">
+        <v>353</v>
+      </c>
+      <c r="B317" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C317" s="9"/>
+      <c r="D317" s="10"/>
+      <c r="E317" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A318" s="142"/>
+      <c r="B318" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C318" s="9"/>
+      <c r="D318" s="10"/>
+      <c r="E318" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A319" s="143"/>
+      <c r="B319" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C319" s="9"/>
+      <c r="D319" s="10"/>
+      <c r="E319" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="14.5" customFormat="1" s="1">
+      <c r="A320" s="9"/>
+      <c r="B320" s="9"/>
+      <c r="C320" s="9"/>
+      <c r="D320" s="10"/>
+      <c r="E320" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A321" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A322" s="144" t="s">
+        <v>357</v>
+      </c>
+      <c r="B322" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="C322" s="9"/>
+      <c r="D322" s="10"/>
+      <c r="E322" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A323" s="145"/>
+      <c r="B323" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="C323" s="9"/>
+      <c r="D323" s="10"/>
+      <c r="E323" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A324" s="145"/>
+      <c r="B324" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C324" s="9"/>
+      <c r="D324" s="10"/>
+      <c r="E324" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A325" s="146"/>
+      <c r="B325" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C325" s="9"/>
+      <c r="D325" s="10"/>
+      <c r="E325" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="30" customFormat="1" s="1">
+      <c r="A326" s="147"/>
+      <c r="B326" s="148" t="s">
+        <v>362</v>
+      </c>
+      <c r="C326" s="147"/>
+      <c r="D326" s="149"/>
+      <c r="E326" s="147"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A327" s="150" t="s">
         <v>148</v>
       </c>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A134" s="51"/>
-      <c r="B134" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A135" s="52"/>
-      <c r="B135" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A136" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A137" s="54"/>
-      <c r="B137" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A138" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A139" s="56"/>
-      <c r="B139" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A140" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A141" s="56"/>
-      <c r="B141" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C141" s="7"/>
-      <c r="D141" s="7"/>
-      <c r="E141" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A142" s="56"/>
-      <c r="B142" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
-      <c r="E142" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A143" s="58"/>
-      <c r="B143" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C143" s="7"/>
-      <c r="D143" s="7"/>
-      <c r="E143" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A144" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A145" s="59" t="s">
-        <v>162</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C145" s="7"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A146" s="60"/>
-      <c r="B146" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A147" s="60"/>
-      <c r="B147" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A148" s="60"/>
-      <c r="B148" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A149" s="61"/>
-      <c r="B149" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A150" s="62" t="s">
-        <v>168</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A151" s="63"/>
-      <c r="B151" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A152" s="63"/>
-      <c r="B152" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A153" s="63"/>
-      <c r="B153" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A154" s="63"/>
-      <c r="B154" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A155" s="63"/>
-      <c r="B155" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A156" s="63"/>
-      <c r="B156" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A157" s="64"/>
-      <c r="B157" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A158" s="65" t="s">
-        <v>177</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A159" s="66"/>
-      <c r="B159" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C159" s="7"/>
-      <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A160" s="66"/>
-      <c r="B160" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C160" s="7"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A161" s="66"/>
-      <c r="B161" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C161" s="7"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A162" s="66"/>
-      <c r="B162" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C162" s="7"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A163" s="67"/>
-      <c r="B163" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C163" s="7"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A164" s="68" t="s">
-        <v>184</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C164" s="7"/>
-      <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A165" s="69"/>
-      <c r="B165" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A166" s="69"/>
-      <c r="B166" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A167" s="69"/>
-      <c r="B167" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C167" s="7"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A168" s="69"/>
-      <c r="B168" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A169" s="69"/>
-      <c r="B169" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A170" s="69"/>
-      <c r="B170" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A171" s="69"/>
-      <c r="B171" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C171" s="7"/>
-      <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A172" s="70"/>
-      <c r="B172" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C172" s="7"/>
-      <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A173" s="71" t="s">
-        <v>194</v>
-      </c>
-      <c r="B173" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C173" s="7"/>
-      <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A174" s="72"/>
-      <c r="B174" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C174" s="7"/>
-      <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A175" s="72"/>
-      <c r="B175" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C175" s="7"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A176" s="72"/>
-      <c r="B176" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C176" s="7"/>
-      <c r="D176" s="7"/>
-      <c r="E176" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A177" s="72"/>
-      <c r="B177" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C177" s="7"/>
-      <c r="D177" s="7"/>
-      <c r="E177" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A178" s="73"/>
-      <c r="B178" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C178" s="7"/>
-      <c r="D178" s="7"/>
-      <c r="E178" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A179" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="B179" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C179" s="7"/>
-      <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A180" s="39"/>
-      <c r="B180" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C180" s="7"/>
-      <c r="D180" s="7"/>
-      <c r="E180" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A181" s="39"/>
-      <c r="B181" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C181" s="7"/>
-      <c r="D181" s="7"/>
-      <c r="E181" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A182" s="39"/>
-      <c r="B182" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C182" s="7"/>
-      <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A183" s="39"/>
-      <c r="B183" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C183" s="7"/>
-      <c r="D183" s="7"/>
-      <c r="E183" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A184" s="40"/>
-      <c r="B184" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C184" s="7"/>
-      <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A185" s="74" t="s">
-        <v>207</v>
-      </c>
-      <c r="B185" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="C185" s="7"/>
-      <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A186" s="75"/>
-      <c r="B186" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C186" s="7"/>
-      <c r="D186" s="7"/>
-      <c r="E186" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A187" s="76" t="s">
-        <v>210</v>
-      </c>
-      <c r="B187" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="C187" s="7"/>
-      <c r="D187" s="7"/>
-      <c r="E187" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A188" s="75"/>
-      <c r="B188" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C188" s="7"/>
-      <c r="D188" s="7"/>
-      <c r="E188" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A189" s="75"/>
-      <c r="B189" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C189" s="7"/>
-      <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A190" s="77"/>
-      <c r="B190" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C190" s="7"/>
-      <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A191" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A192" s="74" t="s">
-        <v>184</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C192" s="7"/>
-      <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A193" s="75"/>
-      <c r="B193" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C193" s="7"/>
-      <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A194" s="75"/>
-      <c r="B194" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C194" s="7"/>
-      <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A195" s="75"/>
-      <c r="B195" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="C195" s="7"/>
-      <c r="D195" s="7"/>
-      <c r="E195" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A196" s="75"/>
-      <c r="B196" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C196" s="7"/>
-      <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A197" s="77"/>
-      <c r="B197" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C197" s="7"/>
-      <c r="D197" s="7"/>
-      <c r="E197" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A198" s="78" t="s">
-        <v>221</v>
-      </c>
-      <c r="B198" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C198" s="7"/>
-      <c r="D198" s="7"/>
-      <c r="E198" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A199" s="79"/>
-      <c r="B199" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C199" s="7"/>
-      <c r="D199" s="7"/>
-      <c r="E199" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A200" s="79"/>
-      <c r="B200" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C200" s="7"/>
-      <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A201" s="80"/>
-      <c r="B201" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C201" s="7"/>
-      <c r="D201" s="7"/>
-      <c r="E201" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A202" s="62" t="s">
-        <v>226</v>
-      </c>
-      <c r="B202" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C202" s="7"/>
-      <c r="D202" s="7"/>
-      <c r="E202" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A203" s="64"/>
-      <c r="B203" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="C203" s="7"/>
-      <c r="D203" s="7"/>
-      <c r="E203" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A204" s="4"/>
-      <c r="B204" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="C204" s="4"/>
-      <c r="D204" s="4"/>
-      <c r="E204" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A205" s="81" t="s">
-        <v>230</v>
-      </c>
-      <c r="B205" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C205" s="7"/>
-      <c r="D205" s="7"/>
-      <c r="E205" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A206" s="82"/>
-      <c r="B206" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C206" s="7"/>
-      <c r="D206" s="7"/>
-      <c r="E206" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A207" s="83"/>
-      <c r="B207" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C207" s="7"/>
-      <c r="D207" s="7"/>
-      <c r="E207" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A208" s="84" t="s">
-        <v>234</v>
-      </c>
-      <c r="B208" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="C208" s="7"/>
-      <c r="D208" s="7"/>
-      <c r="E208" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A209" s="85"/>
-      <c r="B209" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="C209" s="7"/>
-      <c r="D209" s="7"/>
-      <c r="E209" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A210" s="85"/>
-      <c r="B210" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="C210" s="7"/>
-      <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A211" s="85"/>
-      <c r="B211" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="C211" s="7"/>
-      <c r="D211" s="7"/>
-      <c r="E211" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A212" s="85"/>
-      <c r="B212" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C212" s="7"/>
-      <c r="D212" s="7"/>
-      <c r="E212" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A213" s="85"/>
-      <c r="B213" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="C213" s="7"/>
-      <c r="D213" s="7"/>
-      <c r="E213" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A214" s="86"/>
-      <c r="B214" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C214" s="7"/>
-      <c r="D214" s="7"/>
-      <c r="E214" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A215" s="87" t="s">
-        <v>242</v>
-      </c>
-      <c r="B215" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C215" s="7"/>
-      <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A216" s="88"/>
-      <c r="B216" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C216" s="7"/>
-      <c r="D216" s="7"/>
-      <c r="E216" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A217" s="88"/>
-      <c r="B217" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C217" s="7"/>
-      <c r="D217" s="7"/>
-      <c r="E217" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A218" s="89"/>
-      <c r="B218" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="C218" s="7"/>
-      <c r="D218" s="7"/>
-      <c r="E218" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A219" s="4"/>
-      <c r="B219" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C219" s="4"/>
-      <c r="D219" s="4"/>
-      <c r="E219" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A220" s="90" t="s">
-        <v>248</v>
-      </c>
-      <c r="B220" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C220" s="7"/>
-      <c r="D220" s="7"/>
-      <c r="E220" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A221" s="91"/>
-      <c r="B221" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="C221" s="7"/>
-      <c r="D221" s="7"/>
-      <c r="E221" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A222" s="91"/>
-      <c r="B222" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="C222" s="7"/>
-      <c r="D222" s="7"/>
-      <c r="E222" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A223" s="91"/>
-      <c r="B223" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="C223" s="7"/>
-      <c r="D223" s="7"/>
-      <c r="E223" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A224" s="91"/>
-      <c r="B224" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="C224" s="7"/>
-      <c r="D224" s="7"/>
-      <c r="E224" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A225" s="91"/>
-      <c r="B225" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C225" s="7"/>
-      <c r="D225" s="7"/>
-      <c r="E225" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A226" s="91"/>
-      <c r="B226" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="C226" s="7"/>
-      <c r="D226" s="7"/>
-      <c r="E226" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A227" s="91"/>
-      <c r="B227" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C227" s="7"/>
-      <c r="D227" s="7"/>
-      <c r="E227" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A228" s="92"/>
-      <c r="B228" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="C228" s="7"/>
-      <c r="D228" s="7"/>
-      <c r="E228" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A229" s="93" t="s">
-        <v>258</v>
-      </c>
-      <c r="B229" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="C229" s="7"/>
-      <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A230" s="4"/>
-      <c r="B230" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C230" s="4"/>
-      <c r="D230" s="4"/>
-      <c r="E230" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A231" s="94" t="s">
-        <v>261</v>
-      </c>
-      <c r="B231" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C231" s="7"/>
-      <c r="D231" s="7"/>
-      <c r="E231" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A232" s="95"/>
-      <c r="B232" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="C232" s="7"/>
-      <c r="D232" s="7"/>
-      <c r="E232" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A233" s="96"/>
-      <c r="B233" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="C233" s="7"/>
-      <c r="D233" s="7"/>
-      <c r="E233" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A234" s="7"/>
-      <c r="B234" s="7"/>
-      <c r="C234" s="7"/>
-      <c r="D234" s="7"/>
-      <c r="E234" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A235" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B235" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D235" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A236" s="97" t="s">
-        <v>265</v>
-      </c>
-      <c r="B236" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="C236" s="7"/>
-      <c r="D236" s="7"/>
-      <c r="E236" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A237" s="98"/>
-      <c r="B237" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C237" s="7"/>
-      <c r="D237" s="7"/>
-      <c r="E237" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A238" s="98"/>
-      <c r="B238" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="C238" s="7"/>
-      <c r="D238" s="7"/>
-      <c r="E238" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A239" s="98"/>
-      <c r="B239" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="C239" s="7"/>
-      <c r="D239" s="7"/>
-      <c r="E239" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A240" s="98"/>
-      <c r="B240" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="C240" s="7"/>
-      <c r="D240" s="7"/>
-      <c r="E240" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A241" s="98"/>
-      <c r="B241" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="C241" s="7"/>
-      <c r="D241" s="7"/>
-      <c r="E241" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A242" s="98"/>
-      <c r="B242" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="C242" s="7"/>
-      <c r="D242" s="7"/>
-      <c r="E242" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A243" s="99"/>
-      <c r="B243" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="C243" s="7"/>
-      <c r="D243" s="7"/>
-      <c r="E243" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A244" s="100" t="s">
-        <v>274</v>
-      </c>
-      <c r="B244" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C244" s="7"/>
-      <c r="D244" s="7"/>
-      <c r="E244" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A245" s="101"/>
-      <c r="B245" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C245" s="7"/>
-      <c r="D245" s="7"/>
-      <c r="E245" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A246" s="101"/>
-      <c r="B246" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C246" s="7"/>
-      <c r="D246" s="7"/>
-      <c r="E246" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A247" s="102"/>
-      <c r="B247" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="C247" s="7"/>
-      <c r="D247" s="7"/>
-      <c r="E247" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A248" s="103" t="s">
-        <v>279</v>
-      </c>
-      <c r="B248" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C248" s="7"/>
-      <c r="D248" s="7"/>
-      <c r="E248" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A249" s="104"/>
-      <c r="B249" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="C249" s="7"/>
-      <c r="D249" s="7"/>
-      <c r="E249" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A250" s="104"/>
-      <c r="B250" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="C250" s="7"/>
-      <c r="D250" s="7"/>
-      <c r="E250" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A251" s="104"/>
-      <c r="B251" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C251" s="7"/>
-      <c r="D251" s="7"/>
-      <c r="E251" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A252" s="104"/>
-      <c r="B252" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C252" s="7"/>
-      <c r="D252" s="7"/>
-      <c r="E252" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A253" s="104"/>
-      <c r="B253" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="C253" s="7"/>
-      <c r="D253" s="7"/>
-      <c r="E253" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A254" s="104"/>
-      <c r="B254" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="C254" s="7"/>
-      <c r="D254" s="7"/>
-      <c r="E254" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A255" s="105"/>
-      <c r="B255" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C255" s="7"/>
-      <c r="D255" s="7"/>
-      <c r="E255" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A256" s="106" t="s">
-        <v>288</v>
-      </c>
-      <c r="B256" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="C256" s="7"/>
-      <c r="D256" s="7"/>
-      <c r="E256" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A257" s="107"/>
-      <c r="B257" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C257" s="7"/>
-      <c r="D257" s="7"/>
-      <c r="E257" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A258" s="107"/>
-      <c r="B258" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="C258" s="7"/>
-      <c r="D258" s="7"/>
-      <c r="E258" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A259" s="107"/>
-      <c r="B259" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C259" s="7"/>
-      <c r="D259" s="7"/>
-      <c r="E259" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A260" s="107"/>
-      <c r="B260" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C260" s="7"/>
-      <c r="D260" s="7"/>
-      <c r="E260" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A261" s="107"/>
-      <c r="B261" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="C261" s="7"/>
-      <c r="D261" s="7"/>
-      <c r="E261" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A262" s="107"/>
-      <c r="B262" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C262" s="7"/>
-      <c r="D262" s="7"/>
-      <c r="E262" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A263" s="107"/>
-      <c r="B263" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="C263" s="7"/>
-      <c r="D263" s="7"/>
-      <c r="E263" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A264" s="107"/>
-      <c r="B264" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C264" s="7"/>
-      <c r="D264" s="7"/>
-      <c r="E264" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A265" s="108"/>
-      <c r="B265" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="C265" s="7"/>
-      <c r="D265" s="7"/>
-      <c r="E265" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A266" s="109" t="s">
-        <v>299</v>
-      </c>
-      <c r="B266" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="C266" s="7"/>
-      <c r="D266" s="7"/>
-      <c r="E266" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A267" s="110"/>
-      <c r="B267" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="C267" s="7"/>
-      <c r="D267" s="7"/>
-      <c r="E267" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A268" s="111"/>
-      <c r="B268" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="C268" s="7"/>
-      <c r="D268" s="7"/>
-      <c r="E268" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A269" s="112" t="s">
-        <v>303</v>
-      </c>
-      <c r="B269" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="C269" s="7"/>
-      <c r="D269" s="7"/>
-      <c r="E269" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A270" s="113"/>
-      <c r="B270" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="C270" s="7"/>
-      <c r="D270" s="7"/>
-      <c r="E270" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A271" s="113"/>
-      <c r="B271" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="C271" s="7"/>
-      <c r="D271" s="7"/>
-      <c r="E271" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A272" s="113"/>
-      <c r="B272" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="C272" s="7"/>
-      <c r="D272" s="7"/>
-      <c r="E272" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A273" s="114"/>
-      <c r="B273" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C273" s="7"/>
-      <c r="D273" s="7"/>
-      <c r="E273" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A274" s="115" t="s">
-        <v>309</v>
-      </c>
-      <c r="B274" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="C274" s="7"/>
-      <c r="D274" s="7"/>
-      <c r="E274" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A275" s="116"/>
-      <c r="B275" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="C275" s="7"/>
-      <c r="D275" s="7"/>
-      <c r="E275" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A276" s="117"/>
-      <c r="B276" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="C276" s="7"/>
-      <c r="D276" s="7"/>
-      <c r="E276" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A277" s="7"/>
-      <c r="B277" s="7"/>
-      <c r="C277" s="7"/>
-      <c r="D277" s="7"/>
-      <c r="E277" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A278" s="7"/>
-      <c r="B278" s="7"/>
-      <c r="C278" s="7"/>
-      <c r="D278" s="7"/>
-      <c r="E278" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A279" s="7"/>
-      <c r="B279" s="7"/>
-      <c r="C279" s="7"/>
-      <c r="D279" s="7"/>
-      <c r="E279" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A280" s="7"/>
-      <c r="B280" s="7"/>
-      <c r="C280" s="7"/>
-      <c r="D280" s="7"/>
-      <c r="E280" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A281" s="7"/>
-      <c r="B281" s="7"/>
-      <c r="C281" s="7"/>
-      <c r="D281" s="7"/>
-      <c r="E281" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A282" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A283" s="4"/>
-      <c r="B283" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="C283" s="4"/>
-      <c r="D283" s="4"/>
-      <c r="E283" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A284" s="118" t="s">
-        <v>195</v>
-      </c>
-      <c r="B284" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="C284" s="7"/>
-      <c r="D284" s="7"/>
-      <c r="E284" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A285" s="119" t="s">
-        <v>315</v>
-      </c>
-      <c r="B285" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="C285" s="7"/>
-      <c r="D285" s="7"/>
-      <c r="E285" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A286" s="120"/>
-      <c r="B286" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="C286" s="7"/>
-      <c r="D286" s="7"/>
-      <c r="E286" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A287" s="120"/>
-      <c r="B287" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C287" s="7"/>
-      <c r="D287" s="7"/>
-      <c r="E287" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A288" s="120"/>
-      <c r="B288" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="C288" s="7"/>
-      <c r="D288" s="7"/>
-      <c r="E288" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A289" s="121"/>
-      <c r="B289" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C289" s="7"/>
-      <c r="D289" s="7"/>
-      <c r="E289" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A290" s="122" t="s">
-        <v>321</v>
-      </c>
-      <c r="B290" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C290" s="7"/>
-      <c r="D290" s="7"/>
-      <c r="E290" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A291" s="123" t="s">
-        <v>323</v>
-      </c>
-      <c r="B291" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="C291" s="7"/>
-      <c r="D291" s="7"/>
-      <c r="E291" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A292" s="124"/>
-      <c r="B292" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C292" s="7"/>
-      <c r="D292" s="7"/>
-      <c r="E292" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A293" s="124"/>
-      <c r="B293" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="C293" s="7"/>
-      <c r="D293" s="7"/>
-      <c r="E293" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A294" s="124"/>
-      <c r="B294" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C294" s="7"/>
-      <c r="D294" s="7"/>
-      <c r="E294" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A295" s="125"/>
-      <c r="B295" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C295" s="7"/>
-      <c r="D295" s="7"/>
-      <c r="E295" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A296" s="126" t="s">
-        <v>329</v>
-      </c>
-      <c r="B296" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="C296" s="7"/>
-      <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A297" s="127"/>
-      <c r="B297" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="C297" s="7"/>
-      <c r="D297" s="7"/>
-      <c r="E297" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A298" s="127"/>
-      <c r="B298" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="C298" s="7"/>
-      <c r="D298" s="7"/>
-      <c r="E298" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A299" s="127"/>
-      <c r="B299" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="C299" s="7"/>
-      <c r="D299" s="7"/>
-      <c r="E299" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A300" s="128"/>
-      <c r="B300" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="C300" s="7"/>
-      <c r="D300" s="7"/>
-      <c r="E300" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A301" s="84" t="s">
-        <v>335</v>
-      </c>
-      <c r="B301" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="C301" s="7"/>
-      <c r="D301" s="7"/>
-      <c r="E301" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A302" s="85"/>
-      <c r="B302" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C302" s="7"/>
-      <c r="D302" s="7"/>
-      <c r="E302" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A303" s="85"/>
-      <c r="B303" s="129" t="s">
-        <v>338</v>
-      </c>
-      <c r="C303" s="130"/>
-      <c r="D303" s="131"/>
-      <c r="E303" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A304" s="85"/>
-      <c r="B304" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="C304" s="7"/>
-      <c r="D304" s="7"/>
-      <c r="E304" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A305" s="85"/>
-      <c r="B305" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="C305" s="7"/>
-      <c r="D305" s="7"/>
-      <c r="E305" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A306" s="85"/>
-      <c r="B306" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="C306" s="7"/>
-      <c r="D306" s="7"/>
-      <c r="E306" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A307" s="85"/>
-      <c r="B307" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="C307" s="7"/>
-      <c r="D307" s="7"/>
-      <c r="E307" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A308" s="85"/>
-      <c r="B308" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="C308" s="7"/>
-      <c r="D308" s="7"/>
-      <c r="E308" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A309" s="85"/>
-      <c r="B309" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="C309" s="7"/>
-      <c r="D309" s="7"/>
-      <c r="E309" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A310" s="85"/>
-      <c r="B310" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C310" s="7"/>
-      <c r="D310" s="7"/>
-      <c r="E310" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A311" s="86"/>
-      <c r="B311" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="C311" s="7"/>
-      <c r="D311" s="7"/>
-      <c r="E311" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A312" s="132" t="s">
-        <v>347</v>
-      </c>
-      <c r="B312" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="C312" s="7"/>
-      <c r="D312" s="7"/>
-      <c r="E312" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A313" s="133"/>
-      <c r="B313" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C313" s="7"/>
-      <c r="D313" s="7"/>
-      <c r="E313" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A314" s="133"/>
-      <c r="B314" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="C314" s="7"/>
-      <c r="D314" s="7"/>
-      <c r="E314" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A315" s="133"/>
-      <c r="B315" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="C315" s="7"/>
-      <c r="D315" s="7"/>
-      <c r="E315" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A316" s="133"/>
-      <c r="B316" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="C316" s="7"/>
-      <c r="D316" s="7"/>
-      <c r="E316" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A317" s="134"/>
-      <c r="B317" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="C317" s="7"/>
-      <c r="D317" s="7"/>
-      <c r="E317" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A318" s="135"/>
-      <c r="B318" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="C318" s="7"/>
-      <c r="D318" s="7"/>
-      <c r="E318" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A319" s="136"/>
-      <c r="B319" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="C319" s="7"/>
-      <c r="D319" s="7"/>
-      <c r="E319" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A320" s="136"/>
-      <c r="B320" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C320" s="7"/>
-      <c r="D320" s="7"/>
-      <c r="E320" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A321" s="136"/>
-      <c r="B321" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="C321" s="7"/>
-      <c r="D321" s="7"/>
-      <c r="E321" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A322" s="136"/>
-      <c r="B322" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C322" s="7"/>
-      <c r="D322" s="7"/>
-      <c r="E322" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A323" s="136"/>
-      <c r="B323" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="C323" s="7"/>
-      <c r="D323" s="7"/>
-      <c r="E323" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A324" s="137" t="s">
-        <v>360</v>
-      </c>
-      <c r="B324" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="C324" s="7"/>
-      <c r="D324" s="7"/>
-      <c r="E324" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A325" s="138"/>
-      <c r="B325" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="C325" s="7"/>
-      <c r="D325" s="7"/>
-      <c r="E325" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A326" s="139"/>
-      <c r="B326" s="7" t="s">
+      <c r="B327" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="C326" s="7"/>
-      <c r="D326" s="7"/>
-      <c r="E326" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="14.5" customFormat="1" s="1">
-      <c r="A327" s="7"/>
-      <c r="B327" s="7"/>
-      <c r="C327" s="7"/>
-      <c r="D327" s="7"/>
-      <c r="E327" s="7"/>
+      <c r="C327" s="9"/>
+      <c r="D327" s="10"/>
+      <c r="E327" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A328" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B328" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C328" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D328" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E328" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A328" s="151"/>
+      <c r="B328" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C328" s="9"/>
+      <c r="D328" s="10"/>
+      <c r="E328" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A329" s="140" t="s">
-        <v>364</v>
-      </c>
-      <c r="B329" s="7" t="s">
+      <c r="A329" s="152" t="s">
         <v>365</v>
       </c>
-      <c r="C329" s="7"/>
-      <c r="D329" s="7"/>
-      <c r="E329" s="7"/>
+      <c r="B329" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C329" s="9"/>
+      <c r="D329" s="10"/>
+      <c r="E329" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A330" s="141"/>
-      <c r="B330" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="C330" s="7"/>
-      <c r="D330" s="7"/>
-      <c r="E330" s="7"/>
+      <c r="A330" s="153"/>
+      <c r="B330" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="C330" s="9"/>
+      <c r="D330" s="10"/>
+      <c r="E330" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A331" s="141"/>
-      <c r="B331" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C331" s="7"/>
-      <c r="D331" s="7"/>
-      <c r="E331" s="7"/>
+      <c r="A331" s="153"/>
+      <c r="B331" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="C331" s="9"/>
+      <c r="D331" s="10"/>
+      <c r="E331" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A332" s="142"/>
-      <c r="B332" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C332" s="7"/>
-      <c r="D332" s="7"/>
-      <c r="E332" s="7"/>
+      <c r="A332" s="154"/>
+      <c r="B332" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="C332" s="9"/>
+      <c r="D332" s="10"/>
+      <c r="E332" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A333" s="143"/>
-      <c r="B333" s="144" t="s">
-        <v>369</v>
-      </c>
-      <c r="C333" s="143"/>
-      <c r="D333" s="143"/>
-      <c r="E333" s="143"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A334" s="145" t="s">
-        <v>155</v>
-      </c>
-      <c r="B334" s="7" t="s">
+      <c r="A333" s="5"/>
+      <c r="B333" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="C334" s="7"/>
-      <c r="D334" s="7"/>
-      <c r="E334" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A335" s="146"/>
-      <c r="B335" s="7" t="s">
+      <c r="C333" s="5"/>
+      <c r="D333" s="7"/>
+      <c r="E333" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="32.25" customFormat="1" s="1">
+      <c r="A334" s="144" t="s">
         <v>371</v>
       </c>
-      <c r="C335" s="7"/>
-      <c r="D335" s="7"/>
-      <c r="E335" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A336" s="147" t="s">
+      <c r="B334" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="B336" s="7" t="s">
+      <c r="C334" s="9"/>
+      <c r="D334" s="10"/>
+      <c r="E334" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="32.25" customFormat="1" s="1">
+      <c r="A335" s="145"/>
+      <c r="B335" s="133" t="s">
         <v>373</v>
       </c>
-      <c r="C336" s="7"/>
-      <c r="D336" s="7"/>
-      <c r="E336" s="7"/>
+      <c r="C335" s="134"/>
+      <c r="D335" s="135"/>
+      <c r="E335" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="32.25" customFormat="1" s="1">
+      <c r="A336" s="146"/>
+      <c r="B336" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="C336" s="9"/>
+      <c r="D336" s="10"/>
+      <c r="E336" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A337" s="148"/>
-      <c r="B337" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="C337" s="7"/>
-      <c r="D337" s="7"/>
-      <c r="E337" s="7"/>
+      <c r="A337" s="34" t="s">
+        <v>375</v>
+      </c>
+      <c r="B337" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C337" s="9"/>
+      <c r="D337" s="10"/>
+      <c r="E337" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A338" s="148"/>
-      <c r="B338" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="C338" s="7"/>
-      <c r="D338" s="7"/>
-      <c r="E338" s="7"/>
+      <c r="A338" s="35"/>
+      <c r="B338" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="C338" s="9"/>
+      <c r="D338" s="10"/>
+      <c r="E338" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A339" s="149"/>
-      <c r="B339" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="C339" s="7"/>
-      <c r="D339" s="7"/>
-      <c r="E339" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A340" s="4"/>
-      <c r="B340" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="C340" s="4"/>
-      <c r="D340" s="4"/>
-      <c r="E340" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="32.25" customFormat="1" s="1">
-      <c r="A341" s="140" t="s">
+      <c r="A339" s="35"/>
+      <c r="B339" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="B341" s="7" t="s">
+      <c r="C339" s="9"/>
+      <c r="D339" s="10"/>
+      <c r="E339" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A340" s="35"/>
+      <c r="B340" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="C341" s="7"/>
-      <c r="D341" s="7"/>
-      <c r="E341" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="32.25" customFormat="1" s="1">
-      <c r="A342" s="141"/>
-      <c r="B342" s="129" t="s">
+      <c r="C340" s="9"/>
+      <c r="D340" s="10"/>
+      <c r="E340" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A341" s="37"/>
+      <c r="B341" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="C342" s="130"/>
-      <c r="D342" s="131"/>
-      <c r="E342" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="32.25" customFormat="1" s="1">
-      <c r="A343" s="142"/>
-      <c r="B343" s="7" t="s">
+      <c r="C341" s="9"/>
+      <c r="D341" s="10"/>
+      <c r="E341" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="30" customFormat="1" s="1">
+      <c r="A342" s="5"/>
+      <c r="B342" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="C343" s="7"/>
-      <c r="D343" s="7"/>
-      <c r="E343" s="7"/>
+      <c r="C342" s="5"/>
+      <c r="D342" s="7"/>
+      <c r="E342" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="16.5" customFormat="1" s="1">
+      <c r="A343" s="155" t="s">
+        <v>382</v>
+      </c>
+      <c r="B343" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="C343" s="9"/>
+      <c r="D343" s="10"/>
+      <c r="E343" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A344" s="30" t="s">
-        <v>382</v>
-      </c>
-      <c r="B344" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="C344" s="7"/>
-      <c r="D344" s="7"/>
-      <c r="E344" s="7"/>
+      <c r="A344" s="156"/>
+      <c r="B344" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="C344" s="9"/>
+      <c r="D344" s="10"/>
+      <c r="E344" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A345" s="31"/>
-      <c r="B345" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="C345" s="7"/>
-      <c r="D345" s="7"/>
-      <c r="E345" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A346" s="31"/>
-      <c r="B346" s="7" t="s">
+      <c r="A345" s="157"/>
+      <c r="B345" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="C346" s="7"/>
-      <c r="D346" s="7"/>
-      <c r="E346" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A347" s="31"/>
-      <c r="B347" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="C347" s="7"/>
-      <c r="D347" s="7"/>
-      <c r="E347" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A348" s="33"/>
-      <c r="B348" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="C348" s="7"/>
-      <c r="D348" s="7"/>
-      <c r="E348" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A349" s="4"/>
-      <c r="B349" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="C349" s="4"/>
-      <c r="D349" s="4"/>
-      <c r="E349" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A350" s="150" t="s">
-        <v>389</v>
-      </c>
-      <c r="B350" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="C350" s="7"/>
-      <c r="D350" s="7"/>
-      <c r="E350" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A351" s="151"/>
-      <c r="B351" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C351" s="7"/>
-      <c r="D351" s="7"/>
-      <c r="E351" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="16.5" customFormat="1" s="1">
-      <c r="A352" s="152"/>
-      <c r="B352" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="C352" s="7"/>
-      <c r="D352" s="7"/>
-      <c r="E352" s="7"/>
+      <c r="C345" s="9"/>
+      <c r="D345" s="10"/>
+      <c r="E345" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="A3:A16"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A28:A45"/>
-    <mergeCell ref="A46:A55"/>
-    <mergeCell ref="A57:A73"/>
-    <mergeCell ref="A74:A85"/>
-    <mergeCell ref="A86:A92"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="A98:A102"/>
-    <mergeCell ref="A103:A110"/>
-    <mergeCell ref="A111:A116"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A119:A126"/>
-    <mergeCell ref="A127:A129"/>
-    <mergeCell ref="A130:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A140:A143"/>
-    <mergeCell ref="A145:A149"/>
-    <mergeCell ref="A150:A157"/>
-    <mergeCell ref="A158:A163"/>
-    <mergeCell ref="A164:A172"/>
-    <mergeCell ref="A173:A178"/>
-    <mergeCell ref="A179:A184"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A187:A190"/>
-    <mergeCell ref="A192:A197"/>
-    <mergeCell ref="A198:A201"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A205:A207"/>
-    <mergeCell ref="A208:A214"/>
-    <mergeCell ref="A215:A218"/>
-    <mergeCell ref="A220:A228"/>
-    <mergeCell ref="A231:A233"/>
-    <mergeCell ref="A236:A243"/>
-    <mergeCell ref="A244:A247"/>
-    <mergeCell ref="A248:A255"/>
-    <mergeCell ref="A256:A265"/>
-    <mergeCell ref="A266:A268"/>
-    <mergeCell ref="A269:A273"/>
-    <mergeCell ref="A274:A276"/>
-    <mergeCell ref="A285:A289"/>
-    <mergeCell ref="A291:A295"/>
-    <mergeCell ref="A296:A300"/>
-    <mergeCell ref="A301:A311"/>
-    <mergeCell ref="B303:D303"/>
-    <mergeCell ref="A312:A317"/>
-    <mergeCell ref="A318:A323"/>
-    <mergeCell ref="A324:A326"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="A21:A38"/>
+    <mergeCell ref="A39:A48"/>
+    <mergeCell ref="A50:A66"/>
+    <mergeCell ref="A67:A78"/>
+    <mergeCell ref="A79:A85"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A91:A95"/>
+    <mergeCell ref="A96:A103"/>
+    <mergeCell ref="A104:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A119"/>
+    <mergeCell ref="A120:A122"/>
+    <mergeCell ref="A123:A128"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="A138:A142"/>
+    <mergeCell ref="A143:A150"/>
+    <mergeCell ref="A151:A156"/>
+    <mergeCell ref="A157:A165"/>
+    <mergeCell ref="A166:A171"/>
+    <mergeCell ref="A172:A177"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A180:A183"/>
+    <mergeCell ref="A185:A190"/>
+    <mergeCell ref="A191:A194"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="A198:A200"/>
+    <mergeCell ref="A201:A207"/>
+    <mergeCell ref="A208:A211"/>
+    <mergeCell ref="A213:A221"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A229:A236"/>
+    <mergeCell ref="A237:A240"/>
+    <mergeCell ref="A241:A248"/>
+    <mergeCell ref="A249:A258"/>
+    <mergeCell ref="A259:A261"/>
+    <mergeCell ref="A262:A266"/>
+    <mergeCell ref="A267:A269"/>
+    <mergeCell ref="A278:A282"/>
+    <mergeCell ref="A284:A288"/>
+    <mergeCell ref="A289:A293"/>
+    <mergeCell ref="A294:A304"/>
+    <mergeCell ref="B296:D296"/>
+    <mergeCell ref="A305:A310"/>
+    <mergeCell ref="A311:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A322:A325"/>
+    <mergeCell ref="A327:A328"/>
     <mergeCell ref="A329:A332"/>
-    <mergeCell ref="A334:A335"/>
-    <mergeCell ref="A336:A339"/>
-    <mergeCell ref="A341:A343"/>
-    <mergeCell ref="B342:D342"/>
-    <mergeCell ref="A344:A348"/>
-    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A334:A336"/>
+    <mergeCell ref="B335:D335"/>
+    <mergeCell ref="A337:A341"/>
+    <mergeCell ref="A343:A345"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
